--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,46 +686,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>日本10年国債</t>
+          <t>米国2年国債</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>^TNX</t>
+          <t>^IRX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6,506.48</t>
+          <t>6,671.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>米国2年国債</t>
+          <t>米国10年国債</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>^IRX</t>
+          <t>^TNX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6,671.00</t>
+          <t>6,506.48</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>米国10年国債</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>^TNX</t>
+          <t>^GDAXI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -737,80 +737,80 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ドイツ10年国債</t>
+          <t>上海総合</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>^DE10Y</t>
+          <t>000001.SS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6,506.48</t>
+          <t>取得失敗</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>SENSEX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>^GDAXI</t>
+          <t>^BSESN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6,506.48</t>
+          <t>6,775.80</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>上海総合</t>
+          <t>ボベスパ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>000001.SS</t>
+          <t>^BVSP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>取得失敗</t>
+          <t>6,506.48</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SENSEX</t>
+          <t>WTI原油</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>^BSESN</t>
+          <t>CL=F</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">78,205.98 </t>
+          <t>6,506.48</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ボベスパ</t>
+          <t>金先物</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>^BVSP</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -822,12 +822,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WTI原油</t>
+          <t>天然ガス</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CL=F</t>
+          <t>NG=F</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -839,49 +839,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>金先物</t>
+          <t>銅先物</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>HG=F</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>天然ガス</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>NG=F</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>銅先物</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>HG=F</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
         <is>
           <t>6,506.48</t>
         </is>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -425,21 +425,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ティッカー</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>価格</t>
         </is>
@@ -448,202 +453,240 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>^IXIC</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D2" t="n">
+        <v>21647.61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>ダウ平均</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>^DJI</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D3" t="n">
+        <v>45577.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>S&amp;P500</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>^GSPC</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D4" t="n">
+        <v>6506.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>エヌビディア</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D5" t="n">
+        <v>172.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>アップル</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D6" t="n">
+        <v>247.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>マイクロソフト</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D7" t="n">
+        <v>381.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>アルファベット</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D8" t="n">
+        <v>301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>メタ</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D9" t="n">
+        <v>593.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>アマゾン</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D10" t="n">
+        <v>205.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>テスラ</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D11" t="n">
+        <v>367.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>日経平均</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>^N225</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D12" t="n">
+        <v>53372.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>TOPIX</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>^TOPX</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>取得失敗</t>
         </is>
@@ -652,204 +695,250 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>ドル円</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>JPY=X</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>取得失敗</t>
-        </is>
+      <c r="D14" t="n">
+        <v>159.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>ドルインデックス</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>DX-Y.NYB</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>米国2年国債</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>^IRX</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>6,671.00</t>
-        </is>
+      <c r="D16" t="n">
+        <v>3.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>米国10年国債</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>^TNX</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D17" t="n">
+        <v>4.39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>DAX</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>^GDAXI</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D18" t="n">
+        <v>22380.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>上海総合</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>000001.SS</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>取得失敗</t>
-        </is>
+      <c r="D19" t="n">
+        <v>3957.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>SENSEX</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>^BSESN</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>6,775.80</t>
-        </is>
+      <c r="D20" t="n">
+        <v>74532.96000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>ボベスパ</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>^BVSP</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
-        </is>
+      <c r="D21" t="n">
+        <v>176219.41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>WTI原油</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>CL=F</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>金先物</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>GC=F</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>天然ガス</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>銅先物</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>HG=F</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>6,506.48</t>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
         </is>
       </c>
     </row>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,13 +683,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>^TOPX</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>取得失敗</t>
-        </is>
+          <t>1306.T</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3791</v>
       </c>
     </row>
     <row r="14">
@@ -720,18 +718,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ドルインデックス</t>
+          <t>ユーロ円</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DX-Y.NYB</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>取得失敗</t>
-        </is>
+          <t>EURJPY=X</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>184.25</v>
       </c>
     </row>
     <row r="16">
@@ -742,16 +738,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>米国2年国債</t>
+          <t>ユーロドル</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>^IRX</t>
+          <t>EURUSD=X</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.62</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="17">
@@ -762,16 +758,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>米国10年国債</t>
+          <t>米国2年国債</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>^TNX</t>
+          <t>^IRX</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4.39</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="18">
@@ -782,16 +778,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>米国10年国債</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>^GDAXI</t>
+          <t>^TNX</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22380.19</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="19">
@@ -802,16 +798,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>上海総合</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>000001.SS</t>
+          <t>^GDAXI</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3957.05</v>
+        <v>22380.19</v>
       </c>
     </row>
     <row r="20">
@@ -822,16 +818,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SENSEX</t>
+          <t>上海総合</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>^BSESN</t>
+          <t>000001.SS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>74532.96000000001</v>
+        <v>3957.05</v>
       </c>
     </row>
     <row r="21">
@@ -842,16 +838,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ボベスパ</t>
+          <t>SENSEX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>^BVSP</t>
+          <t>^BSESN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>176219.41</v>
+        <v>74532.96000000001</v>
       </c>
     </row>
     <row r="22">
@@ -862,18 +858,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WTI原油</t>
+          <t>ボベスパ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CL=F</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>取得失敗</t>
-        </is>
+          <t>^BVSP</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>176219.41</v>
       </c>
     </row>
     <row r="23">
@@ -884,18 +878,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金先物</t>
+          <t>WTI原油</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GC=F</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>取得失敗</t>
-        </is>
+          <t>CL=F</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>98.23</v>
       </c>
     </row>
     <row r="24">
@@ -906,18 +898,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>天然ガス</t>
+          <t>金先物</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NG=F</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>取得失敗</t>
-        </is>
+          <t>GC=F</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4574.9</v>
       </c>
     </row>
     <row r="25">
@@ -928,18 +918,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>天然ガス</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NG=F</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>銅先物</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>HG=F</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>取得失敗</t>
-        </is>
+      <c r="D26" t="n">
+        <v>5.37</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOPIX</t>
+          <t>ドル円</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1306.T</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3791</v>
+        <v>159.22</v>
       </c>
     </row>
     <row r="14">
@@ -698,16 +698,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ドル円</t>
+          <t>ユーロ円</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>EURJPY=X</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>159.22</v>
+        <v>184.25</v>
       </c>
     </row>
     <row r="15">
@@ -718,16 +718,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ユーロ円</t>
+          <t>ユーロドル</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EURJPY=X</t>
+          <t>EURUSD=X</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>184.25</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="16">
@@ -738,16 +738,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ユーロドル</t>
+          <t>米国2年国債</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EURUSD=X</t>
+          <t>^IRX</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.16</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="17">
@@ -758,16 +758,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>米国2年国債</t>
+          <t>米国10年国債</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>^IRX</t>
+          <t>^TNX</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.62</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="18">
@@ -778,16 +778,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>米国10年国債</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>^TNX</t>
+          <t>^GDAXI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4.39</v>
+        <v>22380.19</v>
       </c>
     </row>
     <row r="19">
@@ -798,16 +798,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>上海総合</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>^GDAXI</t>
+          <t>000001.SS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>22380.19</v>
+        <v>3957.05</v>
       </c>
     </row>
     <row r="20">
@@ -818,16 +818,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>上海総合</t>
+          <t>SENSEX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>000001.SS</t>
+          <t>^BSESN</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3957.05</v>
+        <v>74532.96000000001</v>
       </c>
     </row>
     <row r="21">
@@ -838,16 +838,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SENSEX</t>
+          <t>ボベスパ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>^BSESN</t>
+          <t>^BVSP</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>74532.96000000001</v>
+        <v>176219.41</v>
       </c>
     </row>
     <row r="22">
@@ -858,16 +858,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ボベスパ</t>
+          <t>WTI原油</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>^BVSP</t>
+          <t>CL=F</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>176219.41</v>
+        <v>98.23</v>
       </c>
     </row>
     <row r="23">
@@ -878,16 +878,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WTI原油</t>
+          <t>金先物</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CL=F</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>98.23</v>
+        <v>4574.9</v>
       </c>
     </row>
     <row r="24">
@@ -898,16 +898,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>金先物</t>
+          <t>天然ガス</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>NG=F</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4574.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -918,35 +918,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>天然ガス</t>
+          <t>銅先物</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NG=F</t>
+          <t>HG=F</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>銅先物</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>HG=F</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
         <v>5.37</v>
       </c>
     </row>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-22 08:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-22 08:34</t>
+          <t>2026-03-22 08:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-22 08:36</t>
+          <t>2026-03-22 17:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-22 17:42</t>
+          <t>2026-03-22 18:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -527,13 +527,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>172.7</v>
+        <v>172.93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>381.87</v>
+        <v>381.85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>159.22</v>
+        <v>159.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>184.25</v>
+        <v>184.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>98.23</v>
+        <v>97.93000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4574.9</v>
+        <v>4507.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-22 18:03</t>
+          <t>2026-03-23 07:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.37</v>
+        <v>5.3</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53372.53</v>
+        <v>51515.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>159.3</v>
+        <v>159.53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>184.14</v>
+        <v>183.91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3957.05</v>
+        <v>3807.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>74532.96000000001</v>
+        <v>72744.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>97.93000000000001</v>
+        <v>100.45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4507.5</v>
+        <v>4212.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-23 07:56</t>
+          <t>2026-03-23 15:53</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.3</v>
+        <v>5.27</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>159.53</v>
+        <v>159.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>183.91</v>
+        <v>183.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22380.19</v>
+        <v>21886.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3807.74</v>
+        <v>3813.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>72744.25</v>
+        <v>72696.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>100.45</v>
+        <v>99.14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4212.9</v>
+        <v>4270.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-23 15:53</t>
+          <t>2026-03-23 19:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.27</v>
+        <v>5.31</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21647.61</v>
+        <v>21946.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>45577.47</v>
+        <v>46208.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6506.48</v>
+        <v>6581</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -527,13 +527,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>172.93</v>
+        <v>175.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>247.99</v>
+        <v>251.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>381.85</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>302.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>593.66</v>
+        <v>604.0599999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>205.37</v>
+        <v>210.14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>367.96</v>
+        <v>380.85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>159.59</v>
+        <v>158.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>183.32</v>
+        <v>183.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>21886.18</v>
+        <v>22653.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>176219.41</v>
+        <v>181931.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>99.14</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4270.7</v>
+        <v>4431.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-23 19:40</t>
+          <t>2026-03-24 08:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>51515.49</v>
+        <v>52023.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>158.3</v>
+        <v>158.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>183.86</v>
+        <v>183.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3813.28</v>
+        <v>3837.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>72696.39</v>
+        <v>73438.35000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.05</v>
+        <v>91.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4431.8</v>
+        <v>4362.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-24 08:04</t>
+          <t>2026-03-24 15:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.5</v>
+        <v>5.39</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52023.16</v>
+        <v>52252.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>158.64</v>
+        <v>158.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>183.76</v>
+        <v>183.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22653.86</v>
+        <v>22586.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3837.44</v>
+        <v>3881.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>73438.35000000001</v>
+        <v>74068.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>91.22</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4362.5</v>
+        <v>4424.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-24 15:17</t>
+          <t>2026-03-24 19:37</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21946.76</v>
+        <v>21761.89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>46208.47</v>
+        <v>46124.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6581</v>
+        <v>6556.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -527,13 +527,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>175.64</v>
+        <v>175.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>251.49</v>
+        <v>251.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>383</v>
+        <v>372.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>302.06</v>
+        <v>290.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>604.0599999999999</v>
+        <v>592.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>210.14</v>
+        <v>207.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>380.85</v>
+        <v>383.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>158.71</v>
+        <v>158.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>183.9</v>
+        <v>184.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22586.25</v>
+        <v>22636.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>181931.94</v>
+        <v>182509.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.98999999999999</v>
+        <v>88.79000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4424.2</v>
+        <v>4473.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-24 19:37</t>
+          <t>2026-03-25 08:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.42</v>
+        <v>5.53</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52252.28</v>
+        <v>53735.98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>158.68</v>
+        <v>158.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>184.29</v>
+        <v>184.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3881.28</v>
+        <v>3926.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>74068.45</v>
+        <v>75655.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>88.79000000000001</v>
+        <v>89.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4473.9</v>
+        <v>4546</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-25 08:03</t>
+          <t>2026-03-25 15:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.53</v>
+        <v>5.51</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53735.98</v>
+        <v>53749.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>158.99</v>
+        <v>158.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>184.28</v>
+        <v>184.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22636.91</v>
+        <v>23004.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3926.52</v>
+        <v>3931.84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75655.03</v>
+        <v>75273.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.42</v>
+        <v>87.56999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4546</v>
+        <v>4552.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-25 15:17</t>
+          <t>2026-03-25 19:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.51</v>
+        <v>5.53</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21761.89</v>
+        <v>21929.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>46124.06</v>
+        <v>46429.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6556.37</v>
+        <v>6591.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -527,13 +527,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>175.2</v>
+        <v>178.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>251.64</v>
+        <v>252.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>372.74</v>
+        <v>371.04</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>290.44</v>
+        <v>290.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>592.92</v>
+        <v>594.89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>207.24</v>
+        <v>211.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>383.03</v>
+        <v>385.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>158.96</v>
+        <v>159.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>184.34</v>
+        <v>184.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23004.27</v>
+        <v>22957.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>182509.14</v>
+        <v>185424.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>87.56999999999999</v>
+        <v>90.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4552.5</v>
+        <v>4492.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-25 19:34</t>
+          <t>2026-03-26 08:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.53</v>
+        <v>5.51</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53749.62</v>
+        <v>53603.65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>184.24</v>
+        <v>184.19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3931.84</v>
+        <v>3884.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.97</v>
+        <v>92.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4492.6</v>
+        <v>4434.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-26 08:52</t>
+          <t>2026-03-26 15:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.51</v>
+        <v>5.48</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>159.37</v>
+        <v>159.46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>184.19</v>
+        <v>184.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22957.08</v>
+        <v>22669.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3884.42</v>
+        <v>3889.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>92.17</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4434.3</v>
+        <v>4442.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-26 15:49</t>
+          <t>2026-03-26 19:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.48</v>
+        <v>5.53</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,485 +449,1093 @@
           <t>価格</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>前日比%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>前月比%</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>年初来%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>アップル</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>^IXIC</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21929.83</v>
+        <v>252.38</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-7.97</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ダウ平均</t>
+          <t>マイクロソフト</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>^DJI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>46429.49</v>
+        <v>373.03</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-6.88</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-3.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S&amp;P500</t>
+          <t>アルファベット</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6591.9</v>
+        <v>286.53</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>74.19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>エヌビディア</t>
+          <t>アマゾン</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>178.68</v>
+        <v>209.35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>アップル</t>
+          <t>エヌビディア</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>252.62</v>
+        <v>175.71</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-10.15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>54.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>マイクロソフト</t>
+          <t>メタ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>371.04</v>
+        <v>578.46</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-11.43</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-5.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>アルファベット</t>
+          <t>テスラ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>290.93</v>
+        <v>383.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>40.81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>メタ</t>
+          <t>ユナイテッドヘルス</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>594.89</v>
+        <v>274.39</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-45.56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>アマゾン</t>
+          <t>ゴールドマン・サックス</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>211.71</v>
+        <v>838.34</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>49.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>テスラ</t>
+          <t>ホーム・デポ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>385.95</v>
+        <v>332.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-10.96</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-5.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>日経平均</t>
+          <t>マクドナルド</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>^N225</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53603.65</v>
+        <v>312.28</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ドル円</t>
+          <t>ビザ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>159.46</v>
+        <v>307.57</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-9.970000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ユーロ円</t>
+          <t>ジョンソン・エンド・ジョンソン</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EURJPY=X</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>184.36</v>
+        <v>240.41</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="G14" t="n">
+        <v>52.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ユーロドル</t>
+          <t>プロクター・アンド・ギャンブル</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EURUSD=X</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.16</v>
+        <v>144.21</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-11.74</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-11.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>米国2年国債</t>
+          <t>JPモルガン</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>^IRX</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.62</v>
+        <v>293.98</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19.51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>米国10年国債</t>
+          <t>シェブロン</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>^TNX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4.33</v>
+        <v>206.11</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="G17" t="n">
+        <v>28.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>メルク</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>^GDAXI</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22669.03</v>
+        <v>119.48</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="G18" t="n">
+        <v>40.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>上海総合</t>
+          <t>コカ・コーラ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>000001.SS</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3889.08</v>
+        <v>75.34999999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-5.72</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10.73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SENSEX</t>
+          <t>シスコシステムズ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>^BSESN</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75273.45</v>
+        <v>82.48</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G20" t="n">
+        <v>36.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ボベスパ</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>^BVSP</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>185424.28</v>
+        <v>244.62</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WTI原油</t>
+          <t>アメリカン・エキスプレス</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CL=F</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>92.90000000000001</v>
+        <v>300.46</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金先物</t>
+          <t>キャタピラー</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4442.5</v>
+        <v>713.24</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="G23" t="n">
+        <v>111.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>天然ガス</t>
+          <t>ボーイング</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NG=F</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.88</v>
+        <v>197.4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-14.31</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10.56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-26 19:39</t>
+          <t>2026-03-26 22:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>銅先物</t>
+          <t>ウォルマート</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HG=F</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.53</v>
+        <v>123.19</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="G25" t="n">
+        <v>45.86</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ディズニー</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-3.54</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ナイキ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-15.09</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-16.61</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>セールスフォース</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>186.31</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-33.26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>バークシャー・ハサウェイ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BRK-B</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>476.69</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-10.6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>イーライリリー</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>909.9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-11.56</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10.87</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>エクソンモービル</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>163.16</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="G31" t="n">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>アッヴィ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>207.59</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-8.52</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ブロードコム</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>314.65</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-5.31</v>
+      </c>
+      <c r="G33" t="n">
+        <v>76.56999999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1347.35</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-11.74</v>
+      </c>
+      <c r="G34" t="n">
+        <v>92.58</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>コストコ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>982.61</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6.26</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ペプシコ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>152.51</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6.71</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ネットフリックス</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>92.94</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F37" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-4.25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-26 22:52</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>アドビ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>241.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-6.33</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-39.29</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>前月比%</t>
+          <t>前月末比%</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -468,1074 +468,1219 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>アップル</t>
+          <t>ダウ平均</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>^DJI</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>252.38</v>
+        <v>46480.59</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.97</v>
+        <v>-5.1</v>
       </c>
       <c r="G2" t="n">
-        <v>14.42</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>マイクロソフト</t>
+          <t>S&amp;P500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>373.03</v>
+        <v>6566.89</v>
       </c>
       <c r="E3" t="n">
-        <v>0.54</v>
+        <v>-0.38</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.88</v>
+        <v>-4.54</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.61</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>アルファベット</t>
+          <t>ナスダック</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>^IXIC</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>286.53</v>
+        <v>21794.15</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.51</v>
+        <v>-0.62</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.359999999999999</v>
+        <v>-3.86</v>
       </c>
       <c r="G4" t="n">
-        <v>74.19</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>アマゾン</t>
+          <t>ラッセル2000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>^RUT</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>209.35</v>
+        <v>2524.27</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.11</v>
+        <v>-0.48</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.61</v>
+        <v>-4.11</v>
       </c>
       <c r="G5" t="n">
-        <v>4.09</v>
+        <v>21.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>エヌビディア</t>
+          <t>SOX指数</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>^SOX</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>175.71</v>
+        <v>7765.65</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.66</v>
+        <v>-2.54</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.15</v>
+        <v>-4.11</v>
       </c>
       <c r="G6" t="n">
-        <v>54.49</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>メタ</t>
+          <t>アップル</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>578.46</v>
+        <v>254.1</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.76</v>
+        <v>0.59</v>
       </c>
       <c r="F7" t="n">
-        <v>-11.43</v>
+        <v>-3.82</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.03</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>テスラ</t>
+          <t>マイクロソフト</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>383.1</v>
+        <v>374.42</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.74</v>
+        <v>0.91</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.220000000000001</v>
+        <v>-4.66</v>
       </c>
       <c r="G8" t="n">
-        <v>40.81</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ユナイテッドヘルス</t>
+          <t>アルファベット</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>274.39</v>
+        <v>286.51</v>
       </c>
       <c r="E9" t="n">
-        <v>1.42</v>
+        <v>-1.52</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-45.56</v>
+        <v>74.18000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ゴールドマン・サックス</t>
+          <t>アマゾン</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>838.34</v>
+        <v>211</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.42</v>
+        <v>-0.34</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.529999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="G10" t="n">
-        <v>49.1</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ホーム・デポ</t>
+          <t>エヌビディア</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>332.2</v>
+        <v>175.74</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.09</v>
+        <v>-1.65</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.96</v>
+        <v>-0.82</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.95</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>マクドナルド</t>
+          <t>メタ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>312.28</v>
+        <v>577.61</v>
       </c>
       <c r="E12" t="n">
-        <v>0.19</v>
+        <v>-2.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.7</v>
+        <v>-10.81</v>
       </c>
       <c r="G12" t="n">
-        <v>1.89</v>
+        <v>-5.17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ビザ</t>
+          <t>テスラ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>307.57</v>
+        <v>383.76</v>
       </c>
       <c r="E13" t="n">
-        <v>0.87</v>
+        <v>-0.57</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.73</v>
+        <v>-4.66</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.970000000000001</v>
+        <v>41.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ジョンソン・エンド・ジョンソン</t>
+          <t>ユナイテッドヘルス</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>240.41</v>
+        <v>274.18</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>1.34</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.94</v>
+        <v>-5.78</v>
       </c>
       <c r="G14" t="n">
-        <v>52.8</v>
+        <v>-45.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>プロクター・アンド・ギャンブル</t>
+          <t>ゴールドマン・サックス</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>144.21</v>
+        <v>838.71</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>-0.37</v>
       </c>
       <c r="F15" t="n">
-        <v>-11.74</v>
+        <v>-1.91</v>
       </c>
       <c r="G15" t="n">
-        <v>-11.05</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPモルガン</t>
+          <t>ホーム・デポ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>293.98</v>
+        <v>333.14</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.49</v>
+        <v>0.19</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.07</v>
+        <v>-11.91</v>
       </c>
       <c r="G16" t="n">
-        <v>19.51</v>
+        <v>-5.68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>シェブロン</t>
+          <t>マクドナルド</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>206.11</v>
+        <v>312.35</v>
       </c>
       <c r="E17" t="n">
-        <v>0.47</v>
+        <v>0.21</v>
       </c>
       <c r="F17" t="n">
-        <v>11.88</v>
+        <v>-7.91</v>
       </c>
       <c r="G17" t="n">
-        <v>28.23</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>メルク</t>
+          <t>ビザ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>119.48</v>
+        <v>307.56</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09</v>
+        <v>0.87</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.71</v>
+        <v>-3.93</v>
       </c>
       <c r="G18" t="n">
-        <v>40.53</v>
+        <v>-9.970000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>コカ・コーラ</t>
+          <t>ジョンソン・エンド・ジョンソン</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>75.34999999999999</v>
+        <v>239.88</v>
       </c>
       <c r="E19" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.72</v>
+        <v>-3.44</v>
       </c>
       <c r="G19" t="n">
-        <v>10.73</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>シスコシステムズ</t>
+          <t>プロクター・アンド・ギャンブル</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>82.48</v>
+        <v>144.02</v>
       </c>
       <c r="E20" t="n">
-        <v>0.79</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>4.25</v>
+        <v>-13.86</v>
       </c>
       <c r="G20" t="n">
-        <v>36.71</v>
+        <v>-11.17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>JPモルガン</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>244.62</v>
+        <v>294.61</v>
       </c>
       <c r="E21" t="n">
-        <v>1.34</v>
+        <v>-0.27</v>
       </c>
       <c r="F21" t="n">
-        <v>2.98</v>
+        <v>-1.89</v>
       </c>
       <c r="G21" t="n">
-        <v>0.15</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>アメリカン・エキスプレス</t>
+          <t>シェブロン</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>300.46</v>
+        <v>205.4</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.140000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="G22" t="n">
-        <v>10.02</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>キャタピラー</t>
+          <t>メルク</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>713.24</v>
+        <v>119.11</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.96</v>
+        <v>-3.09</v>
       </c>
       <c r="G23" t="n">
-        <v>111.97</v>
+        <v>40.09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ボーイング</t>
+          <t>コカ・コーラ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>197.4</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1</v>
+        <v>0.13</v>
       </c>
       <c r="F24" t="n">
-        <v>-14.31</v>
+        <v>-6.98</v>
       </c>
       <c r="G24" t="n">
-        <v>10.56</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ウォルマート</t>
+          <t>シスコシステムズ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>123.19</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>0.11</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.83</v>
+        <v>4.01</v>
       </c>
       <c r="G25" t="n">
-        <v>45.86</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ディズニー</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>96.15000000000001</v>
+        <v>245.83</v>
       </c>
       <c r="E26" t="n">
-        <v>0.21</v>
+        <v>1.84</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.470000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.54</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ナイキ</t>
+          <t>アメリカン・エキスプレス</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>53.48</v>
+        <v>301.4</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="F27" t="n">
-        <v>-15.09</v>
+        <v>-2.43</v>
       </c>
       <c r="G27" t="n">
-        <v>-16.61</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>セールスフォース</t>
+          <t>キャタピラー</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>186.31</v>
+        <v>712.0700000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>2.39</v>
+        <v>-0.97</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.84</v>
+        <v>-4.14</v>
       </c>
       <c r="G28" t="n">
-        <v>-33.26</v>
+        <v>111.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>バークシャー・ハサウェイ</t>
+          <t>ボーイング</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>476.69</v>
+        <v>197.21</v>
       </c>
       <c r="E29" t="n">
-        <v>0.11</v>
+        <v>-1.2</v>
       </c>
       <c r="F29" t="n">
-        <v>-3.5</v>
+        <v>-13.32</v>
       </c>
       <c r="G29" t="n">
-        <v>-10.6</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>イーライリリー</t>
+          <t>ウォルマート</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>909.9</v>
+        <v>123.29</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7</v>
+        <v>0.19</v>
       </c>
       <c r="F30" t="n">
-        <v>-11.56</v>
+        <v>-3.44</v>
       </c>
       <c r="G30" t="n">
-        <v>10.87</v>
+        <v>45.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>エクソンモービル</t>
+          <t>ディズニー</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>163.16</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.06</v>
+        <v>0.27</v>
       </c>
       <c r="F31" t="n">
-        <v>9.460000000000001</v>
+        <v>-9.27</v>
       </c>
       <c r="G31" t="n">
-        <v>42.7</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>アッヴィ</t>
+          <t>ナイキ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>207.59</v>
+        <v>53.39</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2</v>
+        <v>0.77</v>
       </c>
       <c r="F32" t="n">
-        <v>-8.52</v>
+        <v>-13.57</v>
       </c>
       <c r="G32" t="n">
-        <v>6.58</v>
+        <v>-16.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ブロードコム</t>
+          <t>セールスフォース</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>314.65</v>
+        <v>186.73</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.3</v>
+        <v>2.62</v>
       </c>
       <c r="F33" t="n">
-        <v>-5.31</v>
+        <v>-4.14</v>
       </c>
       <c r="G33" t="n">
-        <v>76.56999999999999</v>
+        <v>-33.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>バークシャー・ハサウェイ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1347.35</v>
+        <v>478.19</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.34</v>
+        <v>0.42</v>
       </c>
       <c r="F34" t="n">
-        <v>-11.74</v>
+        <v>-5.3</v>
       </c>
       <c r="G34" t="n">
-        <v>92.58</v>
+        <v>-10.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>コストコ</t>
+          <t>イーライリリー</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>982.61</v>
+        <v>907.98</v>
       </c>
       <c r="E35" t="n">
-        <v>0.79</v>
+        <v>-0.91</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.22</v>
+        <v>-13.69</v>
       </c>
       <c r="G35" t="n">
-        <v>6.26</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ペプシコ</t>
+          <t>エクソンモービル</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>152.51</v>
+        <v>162.13</v>
       </c>
       <c r="E36" t="n">
-        <v>0.51</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-9.039999999999999</v>
+        <v>6.32</v>
       </c>
       <c r="G36" t="n">
-        <v>6.71</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ネットフリックス</t>
+          <t>アッヴィ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>92.94</v>
+        <v>207.71</v>
       </c>
       <c r="E37" t="n">
-        <v>0.72</v>
+        <v>0.25</v>
       </c>
       <c r="F37" t="n">
-        <v>12.38</v>
+        <v>-10.5</v>
       </c>
       <c r="G37" t="n">
-        <v>-4.25</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-26 22:52</t>
+          <t>2026-03-26 23:03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>ブロードコム</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>315.51</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="G38" t="n">
+        <v>77.42</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:03</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1340.86</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-7.56</v>
+      </c>
+      <c r="G39" t="n">
+        <v>91.65000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>コストコ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>983.85</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ペプシコ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>152.33</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ネットフリックス</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-3.53</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-26 23:03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>アドビ</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>ADBE</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>241.5</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="F38" t="n">
-        <v>-6.33</v>
-      </c>
-      <c r="G38" t="n">
-        <v>-39.29</v>
+      <c r="D43" t="n">
+        <v>242.82</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-7.46</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-38.96</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46480.59</v>
+        <v>46513.18</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.1</v>
+        <v>-5.03</v>
       </c>
       <c r="G2" t="n">
-        <v>9.48</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -511,22 +511,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6566.89</v>
+        <v>6571.22</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.38</v>
+        <v>-0.31</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.54</v>
+        <v>-4.47</v>
       </c>
       <c r="G3" t="n">
-        <v>14.96</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21794.15</v>
+        <v>21802.43</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.62</v>
+        <v>-0.58</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.86</v>
+        <v>-3.82</v>
       </c>
       <c r="G4" t="n">
-        <v>21.76</v>
+        <v>-6.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,22 +569,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2524.27</v>
+        <v>2527.36</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.48</v>
+        <v>-0.36</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.11</v>
+        <v>-3.99</v>
       </c>
       <c r="G5" t="n">
-        <v>21.72</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7765.65</v>
+        <v>7792.49</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.54</v>
+        <v>-2.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.11</v>
+        <v>-3.78</v>
       </c>
       <c r="G6" t="n">
-        <v>72.23999999999999</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>254.1</v>
+        <v>255.18</v>
       </c>
       <c r="E7" t="n">
-        <v>0.59</v>
+        <v>1.01</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.82</v>
+        <v>-3.41</v>
       </c>
       <c r="G7" t="n">
-        <v>15.2</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>374.42</v>
+        <v>372.21</v>
       </c>
       <c r="E8" t="n">
-        <v>0.91</v>
+        <v>0.32</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.66</v>
+        <v>-5.23</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.25</v>
+        <v>-21.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -685,22 +685,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>286.51</v>
+        <v>287.2</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.52</v>
+        <v>-1.28</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.039999999999999</v>
+        <v>-7.81</v>
       </c>
       <c r="G9" t="n">
-        <v>74.18000000000001</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>211.55</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.34</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="G10" t="n">
-        <v>4.91</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>175.74</v>
+        <v>175.3</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.65</v>
+        <v>-1.89</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.82</v>
+        <v>-1.06</v>
       </c>
       <c r="G11" t="n">
-        <v>54.52</v>
+        <v>-7.17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>577.61</v>
+        <v>575.34</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9</v>
+        <v>-3.29</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.81</v>
+        <v>-11.16</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.17</v>
+        <v>-11.47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>383.76</v>
+        <v>382.82</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.57</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.66</v>
+        <v>-4.89</v>
       </c>
       <c r="G13" t="n">
-        <v>41.06</v>
+        <v>-12.61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>274.18</v>
+        <v>273.14</v>
       </c>
       <c r="E14" t="n">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.78</v>
+        <v>-6.14</v>
       </c>
       <c r="G14" t="n">
-        <v>-45.6</v>
+        <v>-18.17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -859,22 +859,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>838.71</v>
+        <v>836.29</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.37</v>
+        <v>-0.66</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.91</v>
+        <v>-2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>49.16</v>
+        <v>-8.050000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -888,22 +888,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>333.14</v>
+        <v>333.68</v>
       </c>
       <c r="E16" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.91</v>
+        <v>-11.77</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.68</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -917,22 +917,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>312.35</v>
+        <v>312.06</v>
       </c>
       <c r="E17" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.91</v>
+        <v>-7.99</v>
       </c>
       <c r="G17" t="n">
-        <v>1.91</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>307.56</v>
+        <v>306.55</v>
       </c>
       <c r="E18" t="n">
-        <v>0.87</v>
+        <v>0.54</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.93</v>
+        <v>-4.25</v>
       </c>
       <c r="G18" t="n">
-        <v>-9.970000000000001</v>
+        <v>-11.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -975,22 +975,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>239.88</v>
+        <v>240.63</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.02</v>
+        <v>0.29</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.44</v>
+        <v>-3.14</v>
       </c>
       <c r="G19" t="n">
-        <v>52.46</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1004,22 +1004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>144.02</v>
+        <v>143.98</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.86</v>
+        <v>-13.89</v>
       </c>
       <c r="G20" t="n">
-        <v>-11.17</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>294.61</v>
+        <v>294.44</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.27</v>
+        <v>-0.33</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.89</v>
+        <v>-1.95</v>
       </c>
       <c r="G21" t="n">
-        <v>19.77</v>
+        <v>-9.130000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>205.4</v>
+        <v>206.35</v>
       </c>
       <c r="E22" t="n">
-        <v>0.12</v>
+        <v>0.58</v>
       </c>
       <c r="F22" t="n">
-        <v>9.98</v>
+        <v>10.49</v>
       </c>
       <c r="G22" t="n">
-        <v>27.79</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1091,22 +1091,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>119.11</v>
+        <v>119.64</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.22</v>
+        <v>0.23</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.09</v>
+        <v>-2.66</v>
       </c>
       <c r="G23" t="n">
-        <v>40.09</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>75.34999999999999</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.98</v>
+        <v>-6.74</v>
       </c>
       <c r="G24" t="n">
-        <v>10.72</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1149,22 +1149,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>82.65000000000001</v>
+        <v>82.62</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="F25" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="G25" t="n">
-        <v>36.99</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1178,22 +1178,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>245.83</v>
+        <v>245.34</v>
       </c>
       <c r="E26" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="F26" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="G26" t="n">
-        <v>0.64</v>
+        <v>-15.36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1207,22 +1207,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>301.4</v>
+        <v>301.69</v>
       </c>
       <c r="E27" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.43</v>
+        <v>-2.33</v>
       </c>
       <c r="G27" t="n">
-        <v>10.37</v>
+        <v>-19.06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1236,22 +1236,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>712.0700000000001</v>
+        <v>715.48</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.97</v>
+        <v>-0.5</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.14</v>
+        <v>-3.68</v>
       </c>
       <c r="G28" t="n">
-        <v>111.62</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1265,22 +1265,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>197.21</v>
+        <v>197.34</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.2</v>
+        <v>-1.14</v>
       </c>
       <c r="F29" t="n">
-        <v>-13.32</v>
+        <v>-13.27</v>
       </c>
       <c r="G29" t="n">
-        <v>10.45</v>
+        <v>-13.36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1294,22 +1294,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>123.29</v>
+        <v>123.07</v>
       </c>
       <c r="E30" t="n">
-        <v>0.19</v>
+        <v>0.01</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.44</v>
+        <v>-3.62</v>
       </c>
       <c r="G30" t="n">
-        <v>45.98</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>96.20999999999999</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="F31" t="n">
-        <v>-9.27</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>-3.48</v>
+        <v>-13.93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>53.39</v>
+        <v>53.44</v>
       </c>
       <c r="E32" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="F32" t="n">
-        <v>-13.57</v>
+        <v>-13.49</v>
       </c>
       <c r="G32" t="n">
-        <v>-16.75</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>186.73</v>
+        <v>186.35</v>
       </c>
       <c r="E33" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.14</v>
+        <v>-4.34</v>
       </c>
       <c r="G33" t="n">
-        <v>-33.11</v>
+        <v>-26.53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>478.19</v>
+        <v>478.25</v>
       </c>
       <c r="E34" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="F34" t="n">
-        <v>-5.3</v>
+        <v>-5.29</v>
       </c>
       <c r="G34" t="n">
-        <v>-10.32</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>907.98</v>
+        <v>907.67</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.91</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-13.69</v>
+        <v>-13.72</v>
       </c>
       <c r="G35" t="n">
-        <v>10.64</v>
+        <v>-15.84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1468,22 +1468,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>162.13</v>
+        <v>163.33</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="F36" t="n">
-        <v>6.32</v>
+        <v>7.1</v>
       </c>
       <c r="G36" t="n">
-        <v>41.8</v>
+        <v>34.06</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1497,22 +1497,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>207.71</v>
+        <v>208.68</v>
       </c>
       <c r="E37" t="n">
-        <v>0.25</v>
+        <v>0.72</v>
       </c>
       <c r="F37" t="n">
-        <v>-10.5</v>
+        <v>-10.08</v>
       </c>
       <c r="G37" t="n">
-        <v>6.64</v>
+        <v>-8.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1526,22 +1526,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>315.51</v>
+        <v>314.7</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.04</v>
+        <v>-1.29</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.06</v>
+        <v>-1.52</v>
       </c>
       <c r="G38" t="n">
-        <v>77.42</v>
+        <v>-9.470000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1555,22 +1555,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1340.86</v>
+        <v>1350.33</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.8</v>
+        <v>-3.12</v>
       </c>
       <c r="F39" t="n">
-        <v>-7.56</v>
+        <v>-6.91</v>
       </c>
       <c r="G39" t="n">
-        <v>91.65000000000001</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>983.85</v>
+        <v>984.11</v>
       </c>
       <c r="E40" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.67</v>
+        <v>-2.64</v>
       </c>
       <c r="G40" t="n">
-        <v>6.4</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>152.33</v>
+        <v>152.62</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
       <c r="F41" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>6.59</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1642,22 +1642,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>93.64</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.7</v>
+        <v>-3.07</v>
       </c>
       <c r="G42" t="n">
-        <v>-3.53</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-26 23:03</t>
+          <t>2026-03-26 23:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>242.82</v>
+        <v>242.76</v>
       </c>
       <c r="E43" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="F43" t="n">
-        <v>-7.46</v>
+        <v>-7.49</v>
       </c>
       <c r="G43" t="n">
-        <v>-38.96</v>
+        <v>-27.16</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46513.18</v>
+        <v>45960.11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.18</v>
+        <v>-1.01</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.03</v>
+        <v>-6.16</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.86</v>
+        <v>-5.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -511,22 +511,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6571.22</v>
+        <v>6477.16</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.31</v>
+        <v>-1.74</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.47</v>
+        <v>-5.84</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.19</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21802.43</v>
+        <v>21408.08</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.58</v>
+        <v>-2.38</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.82</v>
+        <v>-5.56</v>
       </c>
       <c r="G4" t="n">
-        <v>-6.17</v>
+        <v>-7.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,22 +569,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2527.36</v>
+        <v>2493.32</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.36</v>
+        <v>-1.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.99</v>
+        <v>-5.28</v>
       </c>
       <c r="G5" t="n">
-        <v>0.76</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7792.49</v>
+        <v>7585.87</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2</v>
+        <v>-4.79</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.78</v>
+        <v>-6.33</v>
       </c>
       <c r="G6" t="n">
-        <v>5.77</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>255.18</v>
+        <v>252.89</v>
       </c>
       <c r="E7" t="n">
-        <v>1.01</v>
+        <v>0.11</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.41</v>
+        <v>-4.27</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.75</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>372.21</v>
+        <v>365.97</v>
       </c>
       <c r="E8" t="n">
-        <v>0.32</v>
+        <v>-1.37</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.23</v>
+        <v>-6.82</v>
       </c>
       <c r="G8" t="n">
-        <v>-21.12</v>
+        <v>-22.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -685,22 +685,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>287.2</v>
+        <v>280.92</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.28</v>
+        <v>-3.44</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.81</v>
+        <v>-9.83</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.800000000000001</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>211.55</v>
+        <v>207.54</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.97</v>
       </c>
       <c r="F10" t="n">
-        <v>0.74</v>
+        <v>-1.17</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.6</v>
+        <v>-8.369999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>175.3</v>
+        <v>171.24</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.89</v>
+        <v>-4.16</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.06</v>
+        <v>-3.35</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.17</v>
+        <v>-9.32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>575.34</v>
+        <v>547.54</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.29</v>
+        <v>-7.96</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.16</v>
+        <v>-15.45</v>
       </c>
       <c r="G12" t="n">
-        <v>-11.47</v>
+        <v>-15.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>382.82</v>
+        <v>372.11</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.59</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.89</v>
+        <v>-7.55</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.61</v>
+        <v>-15.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>273.14</v>
+        <v>268.05</v>
       </c>
       <c r="E14" t="n">
-        <v>0.96</v>
+        <v>-0.92</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.14</v>
+        <v>-7.89</v>
       </c>
       <c r="G14" t="n">
-        <v>-18.17</v>
+        <v>-19.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -859,22 +859,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>836.29</v>
+        <v>822.64</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.66</v>
+        <v>-2.28</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2</v>
+        <v>-3.79</v>
       </c>
       <c r="G15" t="n">
-        <v>-8.050000000000001</v>
+        <v>-9.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -888,22 +888,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>333.68</v>
+        <v>328.43</v>
       </c>
       <c r="E16" t="n">
-        <v>0.35</v>
+        <v>-1.23</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.77</v>
+        <v>-13.16</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.86</v>
+        <v>-4.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -917,22 +917,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>312.06</v>
+        <v>308.93</v>
       </c>
       <c r="E17" t="n">
-        <v>0.12</v>
+        <v>-0.89</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.99</v>
+        <v>-8.91</v>
       </c>
       <c r="G17" t="n">
-        <v>3.48</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>306.55</v>
+        <v>305.53</v>
       </c>
       <c r="E18" t="n">
-        <v>0.54</v>
+        <v>0.2</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.25</v>
+        <v>-4.56</v>
       </c>
       <c r="G18" t="n">
-        <v>-11.34</v>
+        <v>-11.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -975,22 +975,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>240.63</v>
+        <v>239.24</v>
       </c>
       <c r="E19" t="n">
-        <v>0.29</v>
+        <v>-0.29</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.14</v>
+        <v>-3.7</v>
       </c>
       <c r="G19" t="n">
-        <v>16.67</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1004,22 +1004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>143.98</v>
+        <v>142.42</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04</v>
+        <v>-1.04</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.89</v>
+        <v>-14.82</v>
       </c>
       <c r="G20" t="n">
-        <v>2.27</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>294.44</v>
+        <v>291.66</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.33</v>
+        <v>-1.27</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.95</v>
+        <v>-2.88</v>
       </c>
       <c r="G21" t="n">
-        <v>-9.130000000000001</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>206.35</v>
+        <v>207.79</v>
       </c>
       <c r="E22" t="n">
-        <v>0.58</v>
+        <v>1.29</v>
       </c>
       <c r="F22" t="n">
-        <v>10.49</v>
+        <v>11.26</v>
       </c>
       <c r="G22" t="n">
-        <v>33.66</v>
+        <v>34.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1091,22 +1091,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>119.64</v>
+        <v>118.93</v>
       </c>
       <c r="E23" t="n">
-        <v>0.23</v>
+        <v>-0.37</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.66</v>
+        <v>-3.24</v>
       </c>
       <c r="G23" t="n">
-        <v>13.22</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>75.54000000000001</v>
+        <v>74.69</v>
       </c>
       <c r="E24" t="n">
-        <v>0.39</v>
+        <v>-0.74</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.74</v>
+        <v>-7.79</v>
       </c>
       <c r="G24" t="n">
-        <v>10.04</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1149,22 +1149,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>82.62</v>
+        <v>82.16</v>
       </c>
       <c r="E25" t="n">
-        <v>0.97</v>
+        <v>0.4</v>
       </c>
       <c r="F25" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="G25" t="n">
-        <v>8.66</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1178,22 +1178,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>245.34</v>
+        <v>241.67</v>
       </c>
       <c r="E26" t="n">
-        <v>1.64</v>
+        <v>0.12</v>
       </c>
       <c r="F26" t="n">
-        <v>2.14</v>
+        <v>0.61</v>
       </c>
       <c r="G26" t="n">
-        <v>-15.36</v>
+        <v>-16.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1207,22 +1207,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>301.69</v>
+        <v>299.39</v>
       </c>
       <c r="E27" t="n">
-        <v>0.48</v>
+        <v>-0.28</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.33</v>
+        <v>-3.08</v>
       </c>
       <c r="G27" t="n">
-        <v>-19.06</v>
+        <v>-19.68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1236,22 +1236,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>715.48</v>
+        <v>703.1900000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5</v>
+        <v>-2.2</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.68</v>
+        <v>-5.34</v>
       </c>
       <c r="G28" t="n">
-        <v>19.84</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1265,22 +1265,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>197.34</v>
+        <v>194.36</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.14</v>
+        <v>-2.63</v>
       </c>
       <c r="F29" t="n">
-        <v>-13.27</v>
+        <v>-14.58</v>
       </c>
       <c r="G29" t="n">
-        <v>-13.36</v>
+        <v>-14.67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1294,22 +1294,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>123.07</v>
+        <v>122.18</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01</v>
+        <v>-0.72</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.62</v>
+        <v>-4.31</v>
       </c>
       <c r="G30" t="n">
-        <v>9.369999999999999</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>96.26000000000001</v>
+        <v>94.75</v>
       </c>
       <c r="E31" t="n">
-        <v>0.33</v>
+        <v>-1.25</v>
       </c>
       <c r="F31" t="n">
-        <v>-9.220000000000001</v>
+        <v>-10.65</v>
       </c>
       <c r="G31" t="n">
-        <v>-13.93</v>
+        <v>-15.29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>53.44</v>
+        <v>52.07</v>
       </c>
       <c r="E32" t="n">
-        <v>0.86</v>
+        <v>-1.72</v>
       </c>
       <c r="F32" t="n">
-        <v>-13.49</v>
+        <v>-15.7</v>
       </c>
       <c r="G32" t="n">
-        <v>-15</v>
+        <v>-17.17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>186.35</v>
+        <v>185.64</v>
       </c>
       <c r="E33" t="n">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.34</v>
+        <v>-4.7</v>
       </c>
       <c r="G33" t="n">
-        <v>-26.53</v>
+        <v>-26.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>478.25</v>
+        <v>475.27</v>
       </c>
       <c r="E34" t="n">
-        <v>0.43</v>
+        <v>-0.19</v>
       </c>
       <c r="F34" t="n">
-        <v>-5.29</v>
+        <v>-5.88</v>
       </c>
       <c r="G34" t="n">
-        <v>-3.74</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>907.67</v>
+        <v>897</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.11</v>
       </c>
       <c r="F35" t="n">
-        <v>-13.72</v>
+        <v>-14.73</v>
       </c>
       <c r="G35" t="n">
-        <v>-15.84</v>
+        <v>-16.83</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1468,22 +1468,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>163.33</v>
+        <v>165.43</v>
       </c>
       <c r="E36" t="n">
-        <v>0.04</v>
+        <v>1.33</v>
       </c>
       <c r="F36" t="n">
-        <v>7.1</v>
+        <v>8.48</v>
       </c>
       <c r="G36" t="n">
-        <v>34.06</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1497,22 +1497,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>208.68</v>
+        <v>211.12</v>
       </c>
       <c r="E37" t="n">
-        <v>0.72</v>
+        <v>1.9</v>
       </c>
       <c r="F37" t="n">
-        <v>-10.08</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>-8.27</v>
+        <v>-7.19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1526,22 +1526,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>314.7</v>
+        <v>309.42</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.29</v>
+        <v>-2.95</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.52</v>
+        <v>-2.97</v>
       </c>
       <c r="G38" t="n">
-        <v>-9.470000000000001</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1555,22 +1555,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1350.33</v>
+        <v>1329.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.12</v>
+        <v>-4.62</v>
       </c>
       <c r="F39" t="n">
-        <v>-6.91</v>
+        <v>-8.35</v>
       </c>
       <c r="G39" t="n">
-        <v>16.18</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>984.11</v>
+        <v>979.65</v>
       </c>
       <c r="E40" t="n">
-        <v>0.95</v>
+        <v>0.49</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.64</v>
+        <v>-3.08</v>
       </c>
       <c r="G40" t="n">
-        <v>15.33</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>152.62</v>
+        <v>150.83</v>
       </c>
       <c r="E41" t="n">
-        <v>0.59</v>
+        <v>-0.59</v>
       </c>
       <c r="F41" t="n">
-        <v>-9.279999999999999</v>
+        <v>-10.35</v>
       </c>
       <c r="G41" t="n">
-        <v>8.26</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1642,22 +1642,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>93.29000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="F42" t="n">
-        <v>-3.07</v>
+        <v>-3.03</v>
       </c>
       <c r="G42" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-26 23:17</t>
+          <t>2026-03-27 08:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>242.76</v>
+        <v>240.88</v>
       </c>
       <c r="E43" t="n">
-        <v>2.32</v>
+        <v>1.53</v>
       </c>
       <c r="F43" t="n">
-        <v>-7.49</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>-27.16</v>
+        <v>-27.73</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1532,16 +1532,16 @@
         <v>-2.95</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.97</v>
+        <v>-3.17</v>
       </c>
       <c r="G38" t="n">
-        <v>-10.8</v>
+        <v>-10.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-27 08:00</t>
+          <t>2026-03-27 15:50</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-27 15:50</t>
+          <t>2026-03-27 19:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45960.11</v>
+        <v>45166.64</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.01</v>
+        <v>-1.73</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.16</v>
+        <v>-7.78</v>
       </c>
       <c r="G2" t="n">
-        <v>-5.01</v>
+        <v>-6.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -511,22 +511,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6477.16</v>
+        <v>6368.85</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.74</v>
+        <v>-1.67</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.84</v>
+        <v>-7.41</v>
       </c>
       <c r="G3" t="n">
-        <v>-5.56</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21408.08</v>
+        <v>20948.36</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.38</v>
+        <v>-2.15</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.56</v>
+        <v>-7.59</v>
       </c>
       <c r="G4" t="n">
-        <v>-7.87</v>
+        <v>-9.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,22 +569,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2493.32</v>
+        <v>2449.7</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7</v>
+        <v>-1.75</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.28</v>
+        <v>-6.94</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.59</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7585.87</v>
+        <v>7457.67</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.79</v>
+        <v>-1.69</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.33</v>
+        <v>-7.91</v>
       </c>
       <c r="G6" t="n">
-        <v>2.96</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>252.89</v>
+        <v>248.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.11</v>
+        <v>-1.62</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.27</v>
+        <v>-5.82</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.6</v>
+        <v>-8.109999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>365.97</v>
+        <v>356.77</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.37</v>
+        <v>-2.51</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.82</v>
+        <v>-9.16</v>
       </c>
       <c r="G8" t="n">
-        <v>-22.44</v>
+        <v>-24.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -685,22 +685,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>280.92</v>
+        <v>274.34</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.44</v>
+        <v>-2.34</v>
       </c>
       <c r="F9" t="n">
-        <v>-9.83</v>
+        <v>-11.94</v>
       </c>
       <c r="G9" t="n">
-        <v>-10.8</v>
+        <v>-12.89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>207.54</v>
+        <v>199.34</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.97</v>
+        <v>-3.95</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.17</v>
+        <v>-5.08</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.369999999999999</v>
+        <v>-11.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>171.24</v>
+        <v>167.52</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.16</v>
+        <v>-2.17</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.35</v>
+        <v>-5.45</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.32</v>
+        <v>-11.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>547.54</v>
+        <v>525.72</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.96</v>
+        <v>-3.99</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.45</v>
+        <v>-18.82</v>
       </c>
       <c r="G12" t="n">
-        <v>-15.74</v>
+        <v>-19.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>372.11</v>
+        <v>361.83</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.59</v>
+        <v>-2.76</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.55</v>
+        <v>-10.11</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.06</v>
+        <v>-17.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>268.05</v>
+        <v>259.02</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.92</v>
+        <v>-3.37</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.89</v>
+        <v>-10.99</v>
       </c>
       <c r="G14" t="n">
-        <v>-19.7</v>
+        <v>-22.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -859,22 +859,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>822.64</v>
+        <v>802.89</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.28</v>
+        <v>-2.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.79</v>
+        <v>-6.1</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.56</v>
+        <v>-11.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -888,22 +888,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>328.43</v>
+        <v>321.65</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.23</v>
+        <v>-2.06</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.16</v>
+        <v>-14.95</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.39</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -917,22 +917,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>308.93</v>
+        <v>305.9</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.89</v>
+        <v>-0.98</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.91</v>
+        <v>-9.81</v>
       </c>
       <c r="G17" t="n">
-        <v>2.44</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>305.53</v>
+        <v>295.52</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2</v>
+        <v>-3.28</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.56</v>
+        <v>-7.69</v>
       </c>
       <c r="G18" t="n">
-        <v>-11.64</v>
+        <v>-14.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -975,22 +975,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>239.24</v>
+        <v>240.45</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.29</v>
+        <v>0.51</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.7</v>
+        <v>-3.21</v>
       </c>
       <c r="G19" t="n">
-        <v>15.99</v>
+        <v>16.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1004,22 +1004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>142.42</v>
+        <v>142.71</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.04</v>
+        <v>0.2</v>
       </c>
       <c r="F20" t="n">
-        <v>-14.82</v>
+        <v>-14.65</v>
       </c>
       <c r="G20" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>291.66</v>
+        <v>282.84</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.27</v>
+        <v>-3.02</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.88</v>
+        <v>-5.81</v>
       </c>
       <c r="G21" t="n">
-        <v>-9.99</v>
+        <v>-12.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>207.79</v>
+        <v>211.15</v>
       </c>
       <c r="E22" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="F22" t="n">
-        <v>11.26</v>
+        <v>13.06</v>
       </c>
       <c r="G22" t="n">
-        <v>34.59</v>
+        <v>36.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1091,22 +1091,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>118.93</v>
+        <v>119.63</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.37</v>
+        <v>0.59</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.24</v>
+        <v>-2.67</v>
       </c>
       <c r="G23" t="n">
-        <v>12.55</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>74.69</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.74</v>
+        <v>1.37</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.79</v>
+        <v>-6.53</v>
       </c>
       <c r="G24" t="n">
-        <v>8.800000000000001</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1149,22 +1149,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>82.16</v>
+        <v>79.92</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4</v>
+        <v>-2.73</v>
       </c>
       <c r="F25" t="n">
-        <v>3.4</v>
+        <v>0.58</v>
       </c>
       <c r="G25" t="n">
-        <v>8.050000000000001</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1178,22 +1178,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>241.67</v>
+        <v>236.34</v>
       </c>
       <c r="E26" t="n">
-        <v>0.12</v>
+        <v>-2.21</v>
       </c>
       <c r="F26" t="n">
-        <v>0.61</v>
+        <v>-1.61</v>
       </c>
       <c r="G26" t="n">
-        <v>-16.62</v>
+        <v>-18.46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1207,22 +1207,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>299.39</v>
+        <v>292.27</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.28</v>
+        <v>-2.38</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.08</v>
+        <v>-5.38</v>
       </c>
       <c r="G27" t="n">
-        <v>-19.68</v>
+        <v>-21.59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1236,22 +1236,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>703.1900000000001</v>
+        <v>695.4</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.2</v>
+        <v>-1.11</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.34</v>
+        <v>-6.39</v>
       </c>
       <c r="G28" t="n">
-        <v>17.78</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1265,22 +1265,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>194.36</v>
+        <v>190.52</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.63</v>
+        <v>-1.98</v>
       </c>
       <c r="F29" t="n">
-        <v>-14.58</v>
+        <v>-16.27</v>
       </c>
       <c r="G29" t="n">
-        <v>-14.67</v>
+        <v>-16.35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1294,22 +1294,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>122.18</v>
+        <v>122.89</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.72</v>
+        <v>0.58</v>
       </c>
       <c r="F30" t="n">
-        <v>-4.31</v>
+        <v>-3.76</v>
       </c>
       <c r="G30" t="n">
-        <v>8.58</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>94.75</v>
+        <v>92.42</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.25</v>
+        <v>-2.46</v>
       </c>
       <c r="F31" t="n">
-        <v>-10.65</v>
+        <v>-12.84</v>
       </c>
       <c r="G31" t="n">
-        <v>-15.29</v>
+        <v>-17.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>52.07</v>
+        <v>51.37</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.72</v>
+        <v>-1.34</v>
       </c>
       <c r="F32" t="n">
-        <v>-15.7</v>
+        <v>-16.84</v>
       </c>
       <c r="G32" t="n">
-        <v>-17.17</v>
+        <v>-18.28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>185.64</v>
+        <v>179.31</v>
       </c>
       <c r="E33" t="n">
-        <v>2.02</v>
+        <v>-3.41</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.7</v>
+        <v>-7.95</v>
       </c>
       <c r="G33" t="n">
-        <v>-26.8</v>
+        <v>-29.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>475.27</v>
+        <v>468.49</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.19</v>
+        <v>-1.43</v>
       </c>
       <c r="F34" t="n">
-        <v>-5.88</v>
+        <v>-7.22</v>
       </c>
       <c r="G34" t="n">
-        <v>-4.34</v>
+        <v>-5.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>897</v>
+        <v>878.24</v>
       </c>
       <c r="E35" t="n">
-        <v>-2.11</v>
+        <v>-2.09</v>
       </c>
       <c r="F35" t="n">
-        <v>-14.73</v>
+        <v>-16.52</v>
       </c>
       <c r="G35" t="n">
-        <v>-16.83</v>
+        <v>-18.57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1468,22 +1468,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>165.43</v>
+        <v>170.99</v>
       </c>
       <c r="E36" t="n">
-        <v>1.33</v>
+        <v>3.36</v>
       </c>
       <c r="F36" t="n">
-        <v>8.48</v>
+        <v>12.12</v>
       </c>
       <c r="G36" t="n">
-        <v>35.78</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1497,22 +1497,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>211.12</v>
+        <v>209.4</v>
       </c>
       <c r="E37" t="n">
-        <v>1.9</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-9.029999999999999</v>
+        <v>-9.77</v>
       </c>
       <c r="G37" t="n">
-        <v>-7.19</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1526,22 +1526,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>309.42</v>
+        <v>300.68</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.95</v>
+        <v>-2.82</v>
       </c>
       <c r="F38" t="n">
-        <v>-3.17</v>
+        <v>-5.71</v>
       </c>
       <c r="G38" t="n">
-        <v>-10.99</v>
+        <v>-13.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1555,22 +1555,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1329.5</v>
+        <v>1302.47</v>
       </c>
       <c r="E39" t="n">
-        <v>-4.62</v>
+        <v>-2.03</v>
       </c>
       <c r="F39" t="n">
-        <v>-8.35</v>
+        <v>-10.21</v>
       </c>
       <c r="G39" t="n">
-        <v>14.39</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>979.65</v>
+        <v>983.86</v>
       </c>
       <c r="E40" t="n">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.08</v>
+        <v>-2.66</v>
       </c>
       <c r="G40" t="n">
-        <v>14.8</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>150.83</v>
+        <v>153.04</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.59</v>
+        <v>1.47</v>
       </c>
       <c r="F41" t="n">
-        <v>-10.35</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>6.99</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1642,22 +1642,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>93.31999999999999</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>1.13</v>
+        <v>0.12</v>
       </c>
       <c r="F42" t="n">
-        <v>-3.03</v>
+        <v>-2.92</v>
       </c>
       <c r="G42" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-27 19:34</t>
+          <t>2026-03-28 08:06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>240.88</v>
+        <v>234.84</v>
       </c>
       <c r="E43" t="n">
-        <v>1.53</v>
+        <v>-2.51</v>
       </c>
       <c r="F43" t="n">
-        <v>-8.199999999999999</v>
+        <v>-10.51</v>
       </c>
       <c r="G43" t="n">
-        <v>-27.73</v>
+        <v>-29.54</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1532,16 +1532,16 @@
         <v>-2.82</v>
       </c>
       <c r="F38" t="n">
-        <v>-5.71</v>
+        <v>-5.91</v>
       </c>
       <c r="G38" t="n">
-        <v>-13.32</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-28 08:06</t>
+          <t>2026-03-28 15:13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1532,16 +1532,16 @@
         <v>-2.82</v>
       </c>
       <c r="F38" t="n">
-        <v>-5.91</v>
+        <v>-5.71</v>
       </c>
       <c r="G38" t="n">
-        <v>-13.5</v>
+        <v>-13.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-28 15:13</t>
+          <t>2026-03-28 18:55</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-28 18:55</t>
+          <t>2026-03-29 08:02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1532,16 +1532,16 @@
         <v>-2.82</v>
       </c>
       <c r="F38" t="n">
-        <v>-5.71</v>
+        <v>-5.91</v>
       </c>
       <c r="G38" t="n">
-        <v>-13.32</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-29 08:02</t>
+          <t>2026-03-29 15:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-29 15:47</t>
+          <t>2026-03-29 18:56</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-29 18:56</t>
+          <t>2026-03-30 08:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1532,16 +1532,16 @@
         <v>-2.82</v>
       </c>
       <c r="F38" t="n">
-        <v>-5.91</v>
+        <v>-5.71</v>
       </c>
       <c r="G38" t="n">
-        <v>-13.5</v>
+        <v>-13.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-30 08:04</t>
+          <t>2026-03-30 17:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1532,16 +1532,16 @@
         <v>-2.82</v>
       </c>
       <c r="F38" t="n">
-        <v>-5.71</v>
+        <v>-5.91</v>
       </c>
       <c r="G38" t="n">
-        <v>-13.32</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-30 17:12</t>
+          <t>2026-03-30 20:37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45166.64</v>
+        <v>45216.14</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.73</v>
+        <v>0.11</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.78</v>
+        <v>-7.68</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.65</v>
+        <v>-6.54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -511,22 +511,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6368.85</v>
+        <v>6343.72</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.67</v>
+        <v>-0.39</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.41</v>
+        <v>-7.78</v>
       </c>
       <c r="G3" t="n">
-        <v>-7.14</v>
+        <v>-7.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20948.36</v>
+        <v>20794.64</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.15</v>
+        <v>-0.73</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.59</v>
+        <v>-8.27</v>
       </c>
       <c r="G4" t="n">
-        <v>-9.84</v>
+        <v>-10.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,22 +569,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2449.7</v>
+        <v>2414.01</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.75</v>
+        <v>-1.46</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.94</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.33</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7457.67</v>
+        <v>7142.33</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.69</v>
+        <v>-4.23</v>
       </c>
       <c r="F6" t="n">
-        <v>-7.91</v>
+        <v>-11.81</v>
       </c>
       <c r="G6" t="n">
-        <v>1.22</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>248.8</v>
+        <v>246.63</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.62</v>
+        <v>-0.87</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.82</v>
+        <v>-6.64</v>
       </c>
       <c r="G7" t="n">
-        <v>-8.109999999999999</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>356.77</v>
+        <v>358.96</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.51</v>
+        <v>0.61</v>
       </c>
       <c r="F8" t="n">
-        <v>-9.16</v>
+        <v>-8.6</v>
       </c>
       <c r="G8" t="n">
-        <v>-24.39</v>
+        <v>-23.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -685,22 +685,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>274.34</v>
+        <v>273.5</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.34</v>
+        <v>-0.31</v>
       </c>
       <c r="F9" t="n">
-        <v>-11.94</v>
+        <v>-12.21</v>
       </c>
       <c r="G9" t="n">
-        <v>-12.89</v>
+        <v>-13.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>199.34</v>
+        <v>200.95</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.95</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.08</v>
+        <v>-4.31</v>
       </c>
       <c r="G10" t="n">
-        <v>-11.99</v>
+        <v>-11.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>167.52</v>
+        <v>165.17</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.17</v>
+        <v>-1.4</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.45</v>
+        <v>-6.78</v>
       </c>
       <c r="G11" t="n">
-        <v>-11.29</v>
+        <v>-12.53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>525.72</v>
+        <v>536.38</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.99</v>
+        <v>2.03</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.82</v>
+        <v>-17.18</v>
       </c>
       <c r="G12" t="n">
-        <v>-19.1</v>
+        <v>-17.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>361.83</v>
+        <v>355.28</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.76</v>
+        <v>-1.81</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.11</v>
+        <v>-11.73</v>
       </c>
       <c r="G13" t="n">
-        <v>-17.4</v>
+        <v>-18.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>259.02</v>
+        <v>261.79</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.37</v>
+        <v>1.07</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.99</v>
+        <v>-10.04</v>
       </c>
       <c r="G14" t="n">
-        <v>-22.4</v>
+        <v>-21.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -859,22 +859,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>802.89</v>
+        <v>807.6</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.4</v>
+        <v>0.59</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.1</v>
+        <v>-5.55</v>
       </c>
       <c r="G15" t="n">
-        <v>-11.73</v>
+        <v>-11.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -888,22 +888,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>321.65</v>
+        <v>323.5</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.06</v>
+        <v>0.58</v>
       </c>
       <c r="F16" t="n">
-        <v>-14.95</v>
+        <v>-14.46</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.37</v>
+        <v>-5.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -917,22 +917,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>305.9</v>
+        <v>308.53</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.98</v>
+        <v>0.86</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.81</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>1.43</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>295.52</v>
+        <v>299.54</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.28</v>
+        <v>1.36</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.69</v>
+        <v>-6.43</v>
       </c>
       <c r="G18" t="n">
-        <v>-14.53</v>
+        <v>-13.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -975,22 +975,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>240.45</v>
+        <v>242.49</v>
       </c>
       <c r="E19" t="n">
-        <v>0.51</v>
+        <v>0.85</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.21</v>
+        <v>-2.39</v>
       </c>
       <c r="G19" t="n">
-        <v>16.58</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1004,22 +1004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>142.71</v>
+        <v>144.72</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2</v>
+        <v>1.41</v>
       </c>
       <c r="F20" t="n">
-        <v>-14.65</v>
+        <v>-13.44</v>
       </c>
       <c r="G20" t="n">
-        <v>1.36</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>282.84</v>
+        <v>283.77</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.02</v>
+        <v>0.33</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.81</v>
+        <v>-5.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-12.71</v>
+        <v>-12.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>211.15</v>
+        <v>210.71</v>
       </c>
       <c r="E22" t="n">
-        <v>1.62</v>
+        <v>-0.21</v>
       </c>
       <c r="F22" t="n">
-        <v>13.06</v>
+        <v>12.82</v>
       </c>
       <c r="G22" t="n">
-        <v>36.76</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1091,22 +1091,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>119.63</v>
+        <v>118.1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.59</v>
+        <v>-1.28</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.67</v>
+        <v>-3.91</v>
       </c>
       <c r="G23" t="n">
-        <v>13.21</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>75.70999999999999</v>
+        <v>76.27</v>
       </c>
       <c r="E24" t="n">
-        <v>1.37</v>
+        <v>0.74</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.53</v>
+        <v>-5.84</v>
       </c>
       <c r="G24" t="n">
-        <v>10.29</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1149,22 +1149,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79.92</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.73</v>
+        <v>-3.6</v>
       </c>
       <c r="F25" t="n">
-        <v>0.58</v>
+        <v>-3.05</v>
       </c>
       <c r="G25" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1178,22 +1178,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>236.34</v>
+        <v>237.25</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.21</v>
+        <v>0.39</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.61</v>
+        <v>-1.23</v>
       </c>
       <c r="G26" t="n">
-        <v>-18.46</v>
+        <v>-18.15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1207,22 +1207,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>292.27</v>
+        <v>297.49</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.38</v>
+        <v>1.79</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.38</v>
+        <v>-3.69</v>
       </c>
       <c r="G27" t="n">
-        <v>-21.59</v>
+        <v>-20.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1236,22 +1236,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>695.4</v>
+        <v>667.4299999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.11</v>
+        <v>-4.02</v>
       </c>
       <c r="F28" t="n">
-        <v>-6.39</v>
+        <v>-10.15</v>
       </c>
       <c r="G28" t="n">
-        <v>16.48</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1265,22 +1265,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>190.52</v>
+        <v>189.21</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.98</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-16.27</v>
+        <v>-16.84</v>
       </c>
       <c r="G29" t="n">
-        <v>-16.35</v>
+        <v>-16.93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1294,22 +1294,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>122.89</v>
+        <v>123.5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.76</v>
+        <v>-3.28</v>
       </c>
       <c r="G30" t="n">
-        <v>9.210000000000001</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>92.42</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.46</v>
+        <v>2.06</v>
       </c>
       <c r="F31" t="n">
-        <v>-12.84</v>
+        <v>-11.05</v>
       </c>
       <c r="G31" t="n">
-        <v>-17.37</v>
+        <v>-15.67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>51.37</v>
+        <v>51.24</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.34</v>
+        <v>-0.25</v>
       </c>
       <c r="F32" t="n">
-        <v>-16.84</v>
+        <v>-17.05</v>
       </c>
       <c r="G32" t="n">
-        <v>-18.28</v>
+        <v>-18.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>179.31</v>
+        <v>185.03</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.41</v>
+        <v>3.19</v>
       </c>
       <c r="F33" t="n">
-        <v>-7.95</v>
+        <v>-5.01</v>
       </c>
       <c r="G33" t="n">
-        <v>-29.3</v>
+        <v>-27.04</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>468.49</v>
+        <v>474.66</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.43</v>
+        <v>1.32</v>
       </c>
       <c r="F34" t="n">
-        <v>-7.22</v>
+        <v>-6</v>
       </c>
       <c r="G34" t="n">
-        <v>-5.71</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>878.24</v>
+        <v>886.63</v>
       </c>
       <c r="E35" t="n">
-        <v>-2.09</v>
+        <v>0.96</v>
       </c>
       <c r="F35" t="n">
-        <v>-16.52</v>
+        <v>-15.72</v>
       </c>
       <c r="G35" t="n">
-        <v>-18.57</v>
+        <v>-17.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1468,22 +1468,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>170.99</v>
+        <v>171.47</v>
       </c>
       <c r="E36" t="n">
-        <v>3.36</v>
+        <v>0.28</v>
       </c>
       <c r="F36" t="n">
-        <v>12.12</v>
+        <v>12.44</v>
       </c>
       <c r="G36" t="n">
-        <v>40.34</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1497,22 +1497,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>209.4</v>
+        <v>213.12</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="F37" t="n">
-        <v>-9.77</v>
+        <v>-8.17</v>
       </c>
       <c r="G37" t="n">
-        <v>-7.95</v>
+        <v>-6.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1526,22 +1526,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>300.68</v>
+        <v>293.41</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.82</v>
+        <v>-2.42</v>
       </c>
       <c r="F38" t="n">
-        <v>-5.91</v>
+        <v>-8.18</v>
       </c>
       <c r="G38" t="n">
-        <v>-13.5</v>
+        <v>-15.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1555,22 +1555,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1302.47</v>
+        <v>1253.96</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.03</v>
+        <v>-3.72</v>
       </c>
       <c r="F39" t="n">
-        <v>-10.21</v>
+        <v>-13.55</v>
       </c>
       <c r="G39" t="n">
-        <v>12.06</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>983.86</v>
+        <v>996.58</v>
       </c>
       <c r="E40" t="n">
-        <v>0.43</v>
+        <v>1.29</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.66</v>
+        <v>-1.41</v>
       </c>
       <c r="G40" t="n">
-        <v>15.3</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>153.04</v>
+        <v>156.82</v>
       </c>
       <c r="E41" t="n">
-        <v>1.47</v>
+        <v>2.47</v>
       </c>
       <c r="F41" t="n">
-        <v>-9.029999999999999</v>
+        <v>-6.79</v>
       </c>
       <c r="G41" t="n">
-        <v>8.56</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1642,22 +1642,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>93.43000000000001</v>
+        <v>92.97</v>
       </c>
       <c r="E42" t="n">
-        <v>0.12</v>
+        <v>-0.49</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.92</v>
+        <v>-3.4</v>
       </c>
       <c r="G42" t="n">
-        <v>2.68</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-30 20:37</t>
+          <t>2026-03-31 08:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>234.84</v>
+        <v>241.13</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.51</v>
+        <v>2.68</v>
       </c>
       <c r="F43" t="n">
-        <v>-10.51</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>-29.54</v>
+        <v>-27.65</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-31 08:52</t>
+          <t>2026-03-31 15:58</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1532,16 +1532,16 @@
         <v>-2.42</v>
       </c>
       <c r="F38" t="n">
-        <v>-8.18</v>
+        <v>-7.99</v>
       </c>
       <c r="G38" t="n">
-        <v>-15.59</v>
+        <v>-15.42</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-31 15:58</t>
+          <t>2026-03-31 20:13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>45216.14</v>
+        <v>46341.51</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11</v>
+        <v>2.49</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.68</v>
+        <v>-5.38</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.54</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -511,22 +511,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6343.72</v>
+        <v>6528.52</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.39</v>
+        <v>2.91</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.78</v>
+        <v>-5.09</v>
       </c>
       <c r="G3" t="n">
-        <v>-7.51</v>
+        <v>-4.81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20794.64</v>
+        <v>21590.63</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.73</v>
+        <v>3.83</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.27</v>
+        <v>-4.75</v>
       </c>
       <c r="G4" t="n">
-        <v>-10.51</v>
+        <v>-7.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,22 +569,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2414.01</v>
+        <v>2496.37</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.46</v>
+        <v>3.41</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.289999999999999</v>
+        <v>-5.17</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.76</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7142.33</v>
+        <v>7588.2</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.23</v>
+        <v>6.24</v>
       </c>
       <c r="F6" t="n">
-        <v>-11.81</v>
+        <v>-6.3</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.06</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>246.63</v>
+        <v>253.79</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.87</v>
+        <v>2.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.64</v>
+        <v>-3.93</v>
       </c>
       <c r="G7" t="n">
-        <v>-8.91</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>358.96</v>
+        <v>370.17</v>
       </c>
       <c r="E8" t="n">
-        <v>0.61</v>
+        <v>3.12</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.6</v>
+        <v>-5.75</v>
       </c>
       <c r="G8" t="n">
-        <v>-23.93</v>
+        <v>-21.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -685,22 +685,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>273.5</v>
+        <v>287.56</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.31</v>
+        <v>5.14</v>
       </c>
       <c r="F9" t="n">
-        <v>-12.21</v>
+        <v>-7.7</v>
       </c>
       <c r="G9" t="n">
-        <v>-13.15</v>
+        <v>-8.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>200.95</v>
+        <v>208.27</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.64</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.31</v>
+        <v>-0.82</v>
       </c>
       <c r="G10" t="n">
-        <v>-11.28</v>
+        <v>-8.050000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>165.17</v>
+        <v>174.4</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4</v>
+        <v>5.59</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.78</v>
+        <v>-1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>-12.53</v>
+        <v>-7.65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>536.38</v>
+        <v>572.13</v>
       </c>
       <c r="E12" t="n">
-        <v>2.03</v>
+        <v>6.67</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.18</v>
+        <v>-11.66</v>
       </c>
       <c r="G12" t="n">
-        <v>-17.46</v>
+        <v>-11.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>355.28</v>
+        <v>371.75</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.81</v>
+        <v>4.64</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.73</v>
+        <v>-7.64</v>
       </c>
       <c r="G13" t="n">
-        <v>-18.9</v>
+        <v>-15.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>261.79</v>
+        <v>270.59</v>
       </c>
       <c r="E14" t="n">
-        <v>1.07</v>
+        <v>3.36</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.04</v>
+        <v>-7.02</v>
       </c>
       <c r="G14" t="n">
-        <v>-21.57</v>
+        <v>-18.94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -859,22 +859,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>807.6</v>
+        <v>845.99</v>
       </c>
       <c r="E15" t="n">
-        <v>0.59</v>
+        <v>4.75</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.55</v>
+        <v>-1.06</v>
       </c>
       <c r="G15" t="n">
-        <v>-11.21</v>
+        <v>-6.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -888,22 +888,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>323.5</v>
+        <v>328.89</v>
       </c>
       <c r="E16" t="n">
-        <v>0.58</v>
+        <v>1.67</v>
       </c>
       <c r="F16" t="n">
-        <v>-14.46</v>
+        <v>-13.04</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.83</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -917,22 +917,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>308.53</v>
+        <v>310.79</v>
       </c>
       <c r="E17" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.029999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>2.31</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>299.54</v>
+        <v>302.24</v>
       </c>
       <c r="E18" t="n">
-        <v>1.36</v>
+        <v>0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.43</v>
+        <v>-5.59</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.37</v>
+        <v>-12.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -975,22 +975,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>242.49</v>
+        <v>244.44</v>
       </c>
       <c r="E19" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.39</v>
+        <v>-1.61</v>
       </c>
       <c r="G19" t="n">
-        <v>17.57</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1004,22 +1004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>144.72</v>
+        <v>144.44</v>
       </c>
       <c r="E20" t="n">
-        <v>1.41</v>
+        <v>-0.19</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.44</v>
+        <v>-13.61</v>
       </c>
       <c r="G20" t="n">
-        <v>2.79</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>283.77</v>
+        <v>294.16</v>
       </c>
       <c r="E21" t="n">
-        <v>0.33</v>
+        <v>3.66</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.5</v>
+        <v>-2.04</v>
       </c>
       <c r="G21" t="n">
-        <v>-12.42</v>
+        <v>-9.220000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>210.71</v>
+        <v>206.9</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.21</v>
+        <v>-1.81</v>
       </c>
       <c r="F22" t="n">
-        <v>12.82</v>
+        <v>10.78</v>
       </c>
       <c r="G22" t="n">
-        <v>36.48</v>
+        <v>34.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1091,22 +1091,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>118.1</v>
+        <v>120.29</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.28</v>
+        <v>1.85</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.91</v>
+        <v>-2.13</v>
       </c>
       <c r="G23" t="n">
-        <v>11.77</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>76.27</v>
+        <v>76.05</v>
       </c>
       <c r="E24" t="n">
-        <v>0.74</v>
+        <v>-0.29</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.84</v>
+        <v>-6.11</v>
       </c>
       <c r="G24" t="n">
-        <v>11.1</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1149,22 +1149,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>77.04000000000001</v>
+        <v>77.59</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6</v>
+        <v>0.71</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.05</v>
+        <v>-2.35</v>
       </c>
       <c r="G25" t="n">
-        <v>1.32</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1178,22 +1178,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>237.25</v>
+        <v>242.39</v>
       </c>
       <c r="E26" t="n">
-        <v>0.39</v>
+        <v>2.17</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.23</v>
+        <v>0.91</v>
       </c>
       <c r="G26" t="n">
-        <v>-18.15</v>
+        <v>-16.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1207,22 +1207,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>297.49</v>
+        <v>302.48</v>
       </c>
       <c r="E27" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.69</v>
+        <v>-2.08</v>
       </c>
       <c r="G27" t="n">
-        <v>-20.19</v>
+        <v>-18.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1236,22 +1236,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>667.4299999999999</v>
+        <v>708.46</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.02</v>
+        <v>6.15</v>
       </c>
       <c r="F28" t="n">
-        <v>-10.15</v>
+        <v>-4.63</v>
       </c>
       <c r="G28" t="n">
-        <v>11.79</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1265,22 +1265,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>189.21</v>
+        <v>199.03</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6899999999999999</v>
+        <v>5.19</v>
       </c>
       <c r="F29" t="n">
-        <v>-16.84</v>
+        <v>-12.53</v>
       </c>
       <c r="G29" t="n">
-        <v>-16.93</v>
+        <v>-12.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1294,22 +1294,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>123.5</v>
+        <v>124.28</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.28</v>
+        <v>-2.67</v>
       </c>
       <c r="G30" t="n">
-        <v>9.75</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>94.31999999999999</v>
+        <v>96.38</v>
       </c>
       <c r="E31" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="F31" t="n">
-        <v>-11.05</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>-15.67</v>
+        <v>-13.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>51.24</v>
+        <v>52.82</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.25</v>
+        <v>3.08</v>
       </c>
       <c r="F32" t="n">
-        <v>-17.05</v>
+        <v>-14.49</v>
       </c>
       <c r="G32" t="n">
-        <v>-18.49</v>
+        <v>-15.98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>185.03</v>
+        <v>186.67</v>
       </c>
       <c r="E33" t="n">
-        <v>3.19</v>
+        <v>0.89</v>
       </c>
       <c r="F33" t="n">
-        <v>-5.01</v>
+        <v>-4.17</v>
       </c>
       <c r="G33" t="n">
-        <v>-27.04</v>
+        <v>-26.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>474.66</v>
+        <v>479.2</v>
       </c>
       <c r="E34" t="n">
-        <v>1.32</v>
+        <v>0.96</v>
       </c>
       <c r="F34" t="n">
-        <v>-6</v>
+        <v>-5.1</v>
       </c>
       <c r="G34" t="n">
-        <v>-4.47</v>
+        <v>-3.55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>886.63</v>
+        <v>919.77</v>
       </c>
       <c r="E35" t="n">
-        <v>0.96</v>
+        <v>3.74</v>
       </c>
       <c r="F35" t="n">
-        <v>-15.72</v>
+        <v>-12.57</v>
       </c>
       <c r="G35" t="n">
-        <v>-17.8</v>
+        <v>-14.72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1468,22 +1468,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>171.47</v>
+        <v>169.66</v>
       </c>
       <c r="E36" t="n">
-        <v>0.28</v>
+        <v>-1.06</v>
       </c>
       <c r="F36" t="n">
-        <v>12.44</v>
+        <v>11.25</v>
       </c>
       <c r="G36" t="n">
-        <v>40.74</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1497,22 +1497,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>213.12</v>
+        <v>217.49</v>
       </c>
       <c r="E37" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="F37" t="n">
-        <v>-8.17</v>
+        <v>-6.29</v>
       </c>
       <c r="G37" t="n">
-        <v>-6.31</v>
+        <v>-4.39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1526,22 +1526,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>293.41</v>
+        <v>309.51</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.42</v>
+        <v>5.49</v>
       </c>
       <c r="F38" t="n">
-        <v>-7.99</v>
+        <v>-2.94</v>
       </c>
       <c r="G38" t="n">
-        <v>-15.42</v>
+        <v>-10.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1555,22 +1555,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1253.96</v>
+        <v>1320.83</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.72</v>
+        <v>5.33</v>
       </c>
       <c r="F39" t="n">
-        <v>-13.55</v>
+        <v>-8.94</v>
       </c>
       <c r="G39" t="n">
-        <v>7.89</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>996.58</v>
+        <v>996.4299999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>1.29</v>
+        <v>-0.02</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.41</v>
+        <v>-1.42</v>
       </c>
       <c r="G40" t="n">
-        <v>16.79</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>156.82</v>
+        <v>155.29</v>
       </c>
       <c r="E41" t="n">
-        <v>2.47</v>
+        <v>-0.98</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.79</v>
+        <v>-7.7</v>
       </c>
       <c r="G41" t="n">
-        <v>11.24</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1642,22 +1642,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>92.97</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.49</v>
+        <v>3.42</v>
       </c>
       <c r="F42" t="n">
-        <v>-3.4</v>
+        <v>-0.09</v>
       </c>
       <c r="G42" t="n">
-        <v>2.18</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-31 20:13</t>
+          <t>2026-04-01 08:05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>241.13</v>
+        <v>243.08</v>
       </c>
       <c r="E43" t="n">
-        <v>2.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>-8.109999999999999</v>
+        <v>-7.37</v>
       </c>
       <c r="G43" t="n">
-        <v>-27.65</v>
+        <v>-27.07</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-01 08:05</t>
+          <t>2026-04-01 17:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-01 17:04</t>
+          <t>2026-04-01 20:31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46341.51</v>
+        <v>46565.74</v>
       </c>
       <c r="E2" t="n">
-        <v>2.49</v>
+        <v>0.48</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.38</v>
+        <v>0.48</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.22</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -511,22 +511,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6528.52</v>
+        <v>6575.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2.91</v>
+        <v>0.72</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.09</v>
+        <v>0.72</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.81</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21590.63</v>
+        <v>21840.95</v>
       </c>
       <c r="E4" t="n">
-        <v>3.83</v>
+        <v>1.16</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.75</v>
+        <v>1.16</v>
       </c>
       <c r="G4" t="n">
-        <v>-7.08</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,22 +569,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2496.37</v>
+        <v>2512.37</v>
       </c>
       <c r="E5" t="n">
-        <v>3.41</v>
+        <v>0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.17</v>
+        <v>0.64</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.47</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7588.2</v>
+        <v>7802.31</v>
       </c>
       <c r="E6" t="n">
-        <v>6.24</v>
+        <v>2.82</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.3</v>
+        <v>2.82</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>253.79</v>
+        <v>255.63</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9</v>
+        <v>0.73</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.93</v>
+        <v>0.73</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.27</v>
+        <v>-5.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>370.17</v>
+        <v>369.37</v>
       </c>
       <c r="E8" t="n">
-        <v>3.12</v>
+        <v>-0.22</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.75</v>
+        <v>-0.22</v>
       </c>
       <c r="G8" t="n">
-        <v>-21.55</v>
+        <v>-21.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -685,22 +685,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>287.56</v>
+        <v>297.39</v>
       </c>
       <c r="E9" t="n">
-        <v>5.14</v>
+        <v>3.42</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.7</v>
+        <v>3.42</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.69</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>208.27</v>
+        <v>210.57</v>
       </c>
       <c r="E10" t="n">
-        <v>3.64</v>
+        <v>1.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.82</v>
+        <v>1.1</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.050000000000001</v>
+        <v>-7.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>174.4</v>
+        <v>175.75</v>
       </c>
       <c r="E11" t="n">
-        <v>5.59</v>
+        <v>0.77</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.57</v>
+        <v>0.77</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.65</v>
+        <v>-6.93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>572.13</v>
+        <v>579.23</v>
       </c>
       <c r="E12" t="n">
-        <v>6.67</v>
+        <v>1.24</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.66</v>
+        <v>1.24</v>
       </c>
       <c r="G12" t="n">
-        <v>-11.96</v>
+        <v>-10.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>371.75</v>
+        <v>381.26</v>
       </c>
       <c r="E13" t="n">
-        <v>4.64</v>
+        <v>2.56</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.64</v>
+        <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.14</v>
+        <v>-12.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>270.59</v>
+        <v>273.98</v>
       </c>
       <c r="E14" t="n">
-        <v>3.36</v>
+        <v>1.25</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.02</v>
+        <v>1.25</v>
       </c>
       <c r="G14" t="n">
-        <v>-18.94</v>
+        <v>-17.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -859,22 +859,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>845.99</v>
+        <v>860.21</v>
       </c>
       <c r="E15" t="n">
-        <v>4.75</v>
+        <v>1.68</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.06</v>
+        <v>1.68</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.99</v>
+        <v>-5.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -888,22 +888,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>328.89</v>
+        <v>329.56</v>
       </c>
       <c r="E16" t="n">
-        <v>1.67</v>
+        <v>0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.04</v>
+        <v>0.2</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.26</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -917,22 +917,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>310.79</v>
+        <v>307.29</v>
       </c>
       <c r="E17" t="n">
-        <v>0.73</v>
+        <v>-1.13</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.369999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="G17" t="n">
-        <v>3.06</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>302.24</v>
+        <v>298.51</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9</v>
+        <v>-1.23</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.59</v>
+        <v>-1.23</v>
       </c>
       <c r="G18" t="n">
-        <v>-12.59</v>
+        <v>-13.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -975,22 +975,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>244.44</v>
+        <v>244.12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8</v>
+        <v>-0.13</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.61</v>
+        <v>-0.13</v>
       </c>
       <c r="G19" t="n">
-        <v>18.51</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1004,22 +1004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>144.44</v>
+        <v>144.09</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.19</v>
+        <v>-0.24</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.61</v>
+        <v>-0.24</v>
       </c>
       <c r="G20" t="n">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>294.16</v>
+        <v>295.38</v>
       </c>
       <c r="E21" t="n">
-        <v>3.66</v>
+        <v>0.41</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.04</v>
+        <v>0.41</v>
       </c>
       <c r="G21" t="n">
-        <v>-9.220000000000001</v>
+        <v>-8.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>206.9</v>
+        <v>197.41</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.81</v>
+        <v>-4.59</v>
       </c>
       <c r="F22" t="n">
-        <v>10.78</v>
+        <v>-4.59</v>
       </c>
       <c r="G22" t="n">
-        <v>34.01</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1091,22 +1091,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>120.29</v>
+        <v>120.84</v>
       </c>
       <c r="E23" t="n">
-        <v>1.85</v>
+        <v>0.46</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.13</v>
+        <v>0.46</v>
       </c>
       <c r="G23" t="n">
-        <v>13.84</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>76.05</v>
+        <v>76.08</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.29</v>
+        <v>0.04</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.11</v>
+        <v>0.04</v>
       </c>
       <c r="G24" t="n">
-        <v>10.78</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1149,22 +1149,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>77.59</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.35</v>
+        <v>0.44</v>
       </c>
       <c r="G25" t="n">
-        <v>2.04</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1178,22 +1178,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>242.39</v>
+        <v>243.14</v>
       </c>
       <c r="E26" t="n">
-        <v>2.17</v>
+        <v>0.31</v>
       </c>
       <c r="F26" t="n">
-        <v>0.91</v>
+        <v>0.31</v>
       </c>
       <c r="G26" t="n">
-        <v>-16.37</v>
+        <v>-16.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1207,22 +1207,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>302.48</v>
+        <v>301.45</v>
       </c>
       <c r="E27" t="n">
-        <v>1.68</v>
+        <v>-0.34</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.08</v>
+        <v>-0.34</v>
       </c>
       <c r="G27" t="n">
-        <v>-18.85</v>
+        <v>-19.12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1236,22 +1236,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>708.46</v>
+        <v>730.3200000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>6.15</v>
+        <v>3.09</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.63</v>
+        <v>3.09</v>
       </c>
       <c r="G28" t="n">
-        <v>18.67</v>
+        <v>22.33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1265,22 +1265,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>199.03</v>
+        <v>207.32</v>
       </c>
       <c r="E29" t="n">
-        <v>5.19</v>
+        <v>4.17</v>
       </c>
       <c r="F29" t="n">
-        <v>-12.53</v>
+        <v>4.17</v>
       </c>
       <c r="G29" t="n">
-        <v>-12.62</v>
+        <v>-8.98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1294,22 +1294,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>124.28</v>
+        <v>124.74</v>
       </c>
       <c r="E30" t="n">
-        <v>0.63</v>
+        <v>0.37</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.67</v>
+        <v>0.37</v>
       </c>
       <c r="G30" t="n">
-        <v>10.44</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>96.38</v>
+        <v>96.56</v>
       </c>
       <c r="E31" t="n">
-        <v>2.18</v>
+        <v>0.19</v>
       </c>
       <c r="F31" t="n">
-        <v>-9.109999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="G31" t="n">
-        <v>-13.83</v>
+        <v>-13.67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>52.82</v>
+        <v>44.63</v>
       </c>
       <c r="E32" t="n">
-        <v>3.08</v>
+        <v>-15.51</v>
       </c>
       <c r="F32" t="n">
-        <v>-14.49</v>
+        <v>-15.51</v>
       </c>
       <c r="G32" t="n">
-        <v>-15.98</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>186.67</v>
+        <v>186.24</v>
       </c>
       <c r="E33" t="n">
-        <v>0.89</v>
+        <v>-0.23</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.17</v>
+        <v>-0.23</v>
       </c>
       <c r="G33" t="n">
-        <v>-26.4</v>
+        <v>-26.57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>479.2</v>
+        <v>478.5</v>
       </c>
       <c r="E34" t="n">
-        <v>0.96</v>
+        <v>-0.15</v>
       </c>
       <c r="F34" t="n">
-        <v>-5.1</v>
+        <v>-0.15</v>
       </c>
       <c r="G34" t="n">
-        <v>-3.55</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>919.77</v>
+        <v>954.52</v>
       </c>
       <c r="E35" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="F35" t="n">
-        <v>-12.57</v>
+        <v>3.78</v>
       </c>
       <c r="G35" t="n">
-        <v>-14.72</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1468,22 +1468,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>169.66</v>
+        <v>160.78</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.06</v>
+        <v>-5.23</v>
       </c>
       <c r="F36" t="n">
-        <v>11.25</v>
+        <v>-5.23</v>
       </c>
       <c r="G36" t="n">
-        <v>39.25</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1497,22 +1497,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>217.49</v>
+        <v>214.98</v>
       </c>
       <c r="E37" t="n">
-        <v>2.05</v>
+        <v>-1.15</v>
       </c>
       <c r="F37" t="n">
-        <v>-6.29</v>
+        <v>-1.15</v>
       </c>
       <c r="G37" t="n">
-        <v>-4.39</v>
+        <v>-5.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1526,22 +1526,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>309.51</v>
+        <v>313.49</v>
       </c>
       <c r="E38" t="n">
-        <v>5.49</v>
+        <v>1.29</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.94</v>
+        <v>1.29</v>
       </c>
       <c r="G38" t="n">
-        <v>-10.78</v>
+        <v>-9.630000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1555,22 +1555,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1320.83</v>
+        <v>1359.76</v>
       </c>
       <c r="E39" t="n">
-        <v>5.33</v>
+        <v>2.95</v>
       </c>
       <c r="F39" t="n">
-        <v>-8.94</v>
+        <v>2.95</v>
       </c>
       <c r="G39" t="n">
-        <v>13.64</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>996.4299999999999</v>
+        <v>996.5599999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.42</v>
+        <v>0.01</v>
       </c>
       <c r="G40" t="n">
-        <v>16.77</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>155.29</v>
+        <v>154.65</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.98</v>
+        <v>-0.41</v>
       </c>
       <c r="F41" t="n">
-        <v>-7.7</v>
+        <v>-0.41</v>
       </c>
       <c r="G41" t="n">
-        <v>10.16</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1642,22 +1642,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>96.15000000000001</v>
+        <v>95.55</v>
       </c>
       <c r="E42" t="n">
-        <v>3.42</v>
+        <v>-0.62</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.09</v>
+        <v>-0.62</v>
       </c>
       <c r="G42" t="n">
-        <v>5.67</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-01 20:31</t>
+          <t>2026-04-02 08:51</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>243.08</v>
+        <v>241.37</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.7</v>
       </c>
       <c r="F43" t="n">
-        <v>-7.37</v>
+        <v>-0.7</v>
       </c>
       <c r="G43" t="n">
-        <v>-27.07</v>
+        <v>-27.58</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-02 08:51</t>
+          <t>2026-04-02 15:56</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-02 15:56</t>
+          <t>2026-04-02 19:39</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46565.74</v>
+        <v>46504.67</v>
       </c>
       <c r="E2" t="n">
-        <v>0.48</v>
+        <v>-0.13</v>
       </c>
       <c r="F2" t="n">
-        <v>0.48</v>
+        <v>0.35</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.75</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -511,22 +511,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6575.32</v>
+        <v>6582.69</v>
       </c>
       <c r="E3" t="n">
-        <v>0.72</v>
+        <v>0.11</v>
       </c>
       <c r="F3" t="n">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.13</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21840.95</v>
+        <v>21879.18</v>
       </c>
       <c r="E4" t="n">
-        <v>1.16</v>
+        <v>0.18</v>
       </c>
       <c r="F4" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
-        <v>-6</v>
+        <v>-5.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,22 +569,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2512.37</v>
+        <v>2530.04</v>
       </c>
       <c r="E5" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="F5" t="n">
-        <v>0.64</v>
+        <v>1.35</v>
       </c>
       <c r="G5" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7802.31</v>
+        <v>7833.39</v>
       </c>
       <c r="E6" t="n">
-        <v>2.82</v>
+        <v>0.4</v>
       </c>
       <c r="F6" t="n">
-        <v>2.82</v>
+        <v>3.23</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>255.63</v>
+        <v>255.92</v>
       </c>
       <c r="E7" t="n">
-        <v>0.73</v>
+        <v>0.11</v>
       </c>
       <c r="F7" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.59</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>369.37</v>
+        <v>373.46</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.22</v>
+        <v>1.11</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.22</v>
+        <v>0.89</v>
       </c>
       <c r="G8" t="n">
-        <v>-21.72</v>
+        <v>-20.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -685,22 +685,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>297.39</v>
+        <v>295.77</v>
       </c>
       <c r="E9" t="n">
-        <v>3.42</v>
+        <v>-0.54</v>
       </c>
       <c r="F9" t="n">
-        <v>3.42</v>
+        <v>2.86</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.57</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>210.57</v>
+        <v>209.77</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1</v>
+        <v>-0.38</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1</v>
+        <v>0.72</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.03</v>
+        <v>-7.39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>175.75</v>
+        <v>177.39</v>
       </c>
       <c r="E11" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="F11" t="n">
-        <v>0.77</v>
+        <v>1.71</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.93</v>
+        <v>-6.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>579.23</v>
+        <v>574.46</v>
       </c>
       <c r="E12" t="n">
-        <v>1.24</v>
+        <v>-0.82</v>
       </c>
       <c r="F12" t="n">
-        <v>1.24</v>
+        <v>0.41</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.87</v>
+        <v>-11.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>381.26</v>
+        <v>360.59</v>
       </c>
       <c r="E13" t="n">
-        <v>2.56</v>
+        <v>-5.42</v>
       </c>
       <c r="F13" t="n">
-        <v>2.56</v>
+        <v>-3</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.97</v>
+        <v>-17.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>273.98</v>
+        <v>277.26</v>
       </c>
       <c r="E14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="F14" t="n">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>-17.92</v>
+        <v>-16.94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -859,22 +859,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>860.21</v>
+        <v>863.04</v>
       </c>
       <c r="E15" t="n">
-        <v>1.68</v>
+        <v>0.33</v>
       </c>
       <c r="F15" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.42</v>
+        <v>-5.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -888,22 +888,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>329.56</v>
+        <v>321.63</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2</v>
+        <v>-2.41</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2</v>
+        <v>-2.21</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.06</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -917,22 +917,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>307.29</v>
+        <v>307.14</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.13</v>
+        <v>-0.05</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.13</v>
+        <v>-1.17</v>
       </c>
       <c r="G17" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>298.51</v>
+        <v>300.8</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.23</v>
+        <v>0.77</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.23</v>
+        <v>-0.48</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.67</v>
+        <v>-13.01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -975,22 +975,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>244.12</v>
+        <v>243.04</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.13</v>
+        <v>-0.44</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.13</v>
+        <v>-0.57</v>
       </c>
       <c r="G19" t="n">
-        <v>18.36</v>
+        <v>17.84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1004,22 +1004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>144.09</v>
+        <v>143.12</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.24</v>
+        <v>-0.67</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.24</v>
+        <v>-0.91</v>
       </c>
       <c r="G20" t="n">
-        <v>2.34</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>295.38</v>
+        <v>294.6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.41</v>
+        <v>-0.26</v>
       </c>
       <c r="F21" t="n">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.84</v>
+        <v>-9.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>197.41</v>
+        <v>198.97</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.59</v>
+        <v>0.79</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.59</v>
+        <v>-3.83</v>
       </c>
       <c r="G22" t="n">
-        <v>27.86</v>
+        <v>28.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1091,22 +1091,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>120.84</v>
+        <v>120.87</v>
       </c>
       <c r="E23" t="n">
-        <v>0.46</v>
+        <v>0.02</v>
       </c>
       <c r="F23" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="G23" t="n">
-        <v>14.36</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>76.08</v>
+        <v>76.72</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04</v>
+        <v>0.84</v>
       </c>
       <c r="F24" t="n">
-        <v>0.04</v>
+        <v>0.88</v>
       </c>
       <c r="G24" t="n">
-        <v>10.83</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1149,22 +1149,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>77.93000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="E25" t="n">
-        <v>0.44</v>
+        <v>1.4</v>
       </c>
       <c r="F25" t="n">
-        <v>0.44</v>
+        <v>1.84</v>
       </c>
       <c r="G25" t="n">
-        <v>2.49</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1178,22 +1178,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>243.14</v>
+        <v>248.16</v>
       </c>
       <c r="E26" t="n">
-        <v>0.31</v>
+        <v>2.06</v>
       </c>
       <c r="F26" t="n">
-        <v>0.31</v>
+        <v>2.38</v>
       </c>
       <c r="G26" t="n">
-        <v>-16.11</v>
+        <v>-14.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1207,22 +1207,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>301.45</v>
+        <v>300.18</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.34</v>
+        <v>-0.42</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.34</v>
+        <v>-0.76</v>
       </c>
       <c r="G27" t="n">
-        <v>-19.12</v>
+        <v>-19.46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1236,22 +1236,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>730.3200000000001</v>
+        <v>717.22</v>
       </c>
       <c r="E28" t="n">
-        <v>3.09</v>
+        <v>-1.79</v>
       </c>
       <c r="F28" t="n">
-        <v>3.09</v>
+        <v>1.24</v>
       </c>
       <c r="G28" t="n">
-        <v>22.33</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1265,22 +1265,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>207.32</v>
+        <v>208.22</v>
       </c>
       <c r="E29" t="n">
-        <v>4.17</v>
+        <v>0.43</v>
       </c>
       <c r="F29" t="n">
-        <v>4.17</v>
+        <v>4.62</v>
       </c>
       <c r="G29" t="n">
-        <v>-8.98</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1294,22 +1294,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>124.74</v>
+        <v>125.79</v>
       </c>
       <c r="E30" t="n">
-        <v>0.37</v>
+        <v>0.84</v>
       </c>
       <c r="F30" t="n">
-        <v>0.37</v>
+        <v>1.22</v>
       </c>
       <c r="G30" t="n">
-        <v>10.85</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>96.56</v>
+        <v>96.61</v>
       </c>
       <c r="E31" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="G31" t="n">
-        <v>-13.67</v>
+        <v>-13.63</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>44.63</v>
+        <v>44.19</v>
       </c>
       <c r="E32" t="n">
-        <v>-15.51</v>
+        <v>-0.99</v>
       </c>
       <c r="F32" t="n">
-        <v>-15.51</v>
+        <v>-16.34</v>
       </c>
       <c r="G32" t="n">
-        <v>-29</v>
+        <v>-29.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>186.24</v>
+        <v>187.18</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.23</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.23</v>
+        <v>0.27</v>
       </c>
       <c r="G33" t="n">
-        <v>-26.57</v>
+        <v>-26.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>478.5</v>
+        <v>477.35</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.15</v>
+        <v>-0.24</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.15</v>
+        <v>-0.39</v>
       </c>
       <c r="G34" t="n">
-        <v>-3.69</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>954.52</v>
+        <v>935.58</v>
       </c>
       <c r="E35" t="n">
-        <v>3.78</v>
+        <v>-1.98</v>
       </c>
       <c r="F35" t="n">
-        <v>3.78</v>
+        <v>1.72</v>
       </c>
       <c r="G35" t="n">
-        <v>-11.5</v>
+        <v>-13.26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1468,22 +1468,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>160.78</v>
+        <v>160.69</v>
       </c>
       <c r="E36" t="n">
-        <v>-5.23</v>
+        <v>-0.06</v>
       </c>
       <c r="F36" t="n">
-        <v>-5.23</v>
+        <v>-5.29</v>
       </c>
       <c r="G36" t="n">
-        <v>31.96</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1497,22 +1497,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>214.98</v>
+        <v>208.84</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.15</v>
+        <v>-2.86</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.15</v>
+        <v>-3.98</v>
       </c>
       <c r="G37" t="n">
-        <v>-5.49</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1526,22 +1526,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>313.49</v>
+        <v>314.55</v>
       </c>
       <c r="E38" t="n">
-        <v>1.29</v>
+        <v>0.34</v>
       </c>
       <c r="F38" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="G38" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1555,22 +1555,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1359.76</v>
+        <v>1317.23</v>
       </c>
       <c r="E39" t="n">
-        <v>2.95</v>
+        <v>-3.13</v>
       </c>
       <c r="F39" t="n">
-        <v>2.95</v>
+        <v>-0.27</v>
       </c>
       <c r="G39" t="n">
-        <v>16.99</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>996.5599999999999</v>
+        <v>1014.96</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01</v>
+        <v>1.85</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01</v>
+        <v>1.86</v>
       </c>
       <c r="G40" t="n">
-        <v>16.78</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>154.65</v>
+        <v>157.01</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.41</v>
+        <v>1.53</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.41</v>
+        <v>1.11</v>
       </c>
       <c r="G41" t="n">
-        <v>9.699999999999999</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1642,22 +1642,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>95.55</v>
+        <v>98.66</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.62</v>
+        <v>3.25</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.62</v>
+        <v>2.61</v>
       </c>
       <c r="G42" t="n">
-        <v>5.01</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-02 19:39</t>
+          <t>2026-04-03 08:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>241.37</v>
+        <v>242.92</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.7</v>
+        <v>0.64</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.7</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>-27.58</v>
+        <v>-27.12</v>
       </c>
     </row>
   </sheetData>

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1152,19 +1152,19 @@
         <v>79.02</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="F25" t="n">
-        <v>1.84</v>
+        <v>2.39</v>
       </c>
       <c r="G25" t="n">
-        <v>3.92</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1210,19 +1210,19 @@
         <v>300.18</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.42</v>
+        <v>-0.11</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.76</v>
+        <v>-0.45</v>
       </c>
       <c r="G27" t="n">
-        <v>-19.46</v>
+        <v>-19.21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-03 08:04</t>
+          <t>2026-04-03 15:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-03 15:52</t>
+          <t>2026-04-03 19:09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-03 19:09</t>
+          <t>2026-04-04 08:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-04 08:04</t>
+          <t>2026-04-04 15:15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-04 15:15</t>
+          <t>2026-04-04 18:56</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-04 18:56</t>
+          <t>2026-04-05 08:01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-05 08:01</t>
+          <t>2026-04-05 15:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">

--- a/market_data.xlsx
+++ b/market_data.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1454,7 +1454,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1628,7 +1628,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-05 15:47</t>
+          <t>2026-04-05 18:59</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
